--- a/util/Validation/ManualValidation/classListForManual copy.xlsx
+++ b/util/Validation/ManualValidation/classListForManual copy.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10913"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/neda/git/Research/BadSmells/util/Validation/ManualValidation/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/neda/Desktop/workspace/BadSmells/util/Validation/ManualValidation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88FA714D-080C-7048-8728-BA2752364B81}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D32E2529-CCB0-0944-86D7-878FE9B6F36F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8940" yWindow="900" windowWidth="19800" windowHeight="14320" xr2:uid="{3004C773-7DF2-304E-B74E-6C331540559A}"/>
+    <workbookView xWindow="1080" yWindow="660" windowWidth="10640" windowHeight="14320" xr2:uid="{3004C773-7DF2-304E-B74E-6C331540559A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -481,9 +481,6 @@
     <t>_Feature</t>
   </si>
   <si>
-    <t>_Parser</t>
-  </si>
-  <si>
     <t>CCompilerOpt</t>
   </si>
   <si>
@@ -1778,6 +1775,9 @@
   </si>
   <si>
     <t>/Users/neda/git/Research/BadSmells/DemoProjects/numpy/numpy/tests/typing/fail/warnings_and_errors.py</t>
+  </si>
+  <si>
+    <t>_Parse</t>
   </si>
 </sst>
 </file>
@@ -1826,11 +1826,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2149,36 +2150,37 @@
   <dimension ref="A1:H534"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="24.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="43.5" style="3" customWidth="1"/>
+    <col min="2" max="16384" width="10.83203125" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -2205,7 +2207,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -2232,7 +2234,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -2259,7 +2261,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -2286,7 +2288,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="G6" t="s">
         <v>9</v>
       </c>
@@ -2294,7 +2296,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="G7" t="s">
         <v>9</v>
       </c>
@@ -2302,7 +2304,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="G8" t="s">
         <v>9</v>
       </c>
@@ -2310,7 +2312,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="G9" t="s">
         <v>9</v>
       </c>
@@ -2318,7 +2320,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -2336,7 +2338,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>21</v>
       </c>
@@ -2360,7 +2362,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>23</v>
       </c>
@@ -2387,7 +2389,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="13" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="F13" t="str" cm="1">
         <f t="array" ref="F13">IF(AND(NOT(ISBLANK(C13:E13)),OR(C13&gt;=200,(D13+E13)&gt;40)),"Yes","No")</f>
         <v>No</v>
@@ -2399,7 +2401,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>26</v>
       </c>
@@ -2426,7 +2428,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>27</v>
       </c>
@@ -2453,7 +2455,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="16" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="G16" t="s">
         <v>9</v>
       </c>
@@ -2461,7 +2463,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="17" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="G17" t="s">
         <v>9</v>
       </c>
@@ -2469,7 +2471,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="G18" t="s">
         <v>9</v>
       </c>
@@ -2477,7 +2479,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="19" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="G19" t="s">
         <v>9</v>
       </c>
@@ -2485,7 +2487,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="20" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="G20" t="s">
         <v>9</v>
       </c>
@@ -2493,7 +2495,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="21" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>34</v>
       </c>
@@ -2520,7 +2522,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="22" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>35</v>
       </c>
@@ -2547,7 +2549,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="23" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="G23" t="s">
         <v>9</v>
       </c>
@@ -2555,7 +2557,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="24" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="G24" t="s">
         <v>9</v>
       </c>
@@ -2563,7 +2565,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="25" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="G25" t="s">
         <v>9</v>
       </c>
@@ -2571,7 +2573,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="26" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="G26" t="s">
         <v>9</v>
       </c>
@@ -2579,7 +2581,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="G27" t="s">
         <v>9</v>
       </c>
@@ -2587,7 +2589,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="G28" t="s">
         <v>9</v>
       </c>
@@ -2595,7 +2597,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>43</v>
       </c>
@@ -2622,7 +2624,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>44</v>
       </c>
@@ -2649,7 +2651,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>45</v>
       </c>
@@ -2676,7 +2678,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>46</v>
       </c>
@@ -2703,7 +2705,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="33" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>47</v>
       </c>
@@ -2730,7 +2732,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="34" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>48</v>
       </c>
@@ -2757,7 +2759,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="35" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>49</v>
       </c>
@@ -2784,7 +2786,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="36" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>50</v>
       </c>
@@ -2811,7 +2813,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="37" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>51</v>
       </c>
@@ -2838,7 +2840,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="38" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>53</v>
       </c>
@@ -2865,7 +2867,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="39" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>54</v>
       </c>
@@ -2892,7 +2894,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="40" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>55</v>
       </c>
@@ -2919,7 +2921,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="41" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>56</v>
       </c>
@@ -2946,7 +2948,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="42" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>57</v>
       </c>
@@ -2973,7 +2975,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="43" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>58</v>
       </c>
@@ -3000,7 +3002,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="44" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="G44" t="s">
         <v>9</v>
       </c>
@@ -3008,7 +3010,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="45" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="G45" t="s">
         <v>9</v>
       </c>
@@ -3016,7 +3018,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="46" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="G46" t="s">
         <v>9</v>
       </c>
@@ -3024,7 +3026,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="47" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>63</v>
       </c>
@@ -3051,7 +3053,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="48" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>64</v>
       </c>
@@ -3078,7 +3080,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="49" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>66</v>
       </c>
@@ -3105,7 +3107,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="50" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>67</v>
       </c>
@@ -3132,7 +3134,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="51" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>68</v>
       </c>
@@ -3159,7 +3161,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="52" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>69</v>
       </c>
@@ -3186,7 +3188,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="53" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>70</v>
       </c>
@@ -3213,7 +3215,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="54" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>71</v>
       </c>
@@ -3240,7 +3242,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="55" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>72</v>
       </c>
@@ -3267,7 +3269,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="56" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>73</v>
       </c>
@@ -3294,7 +3296,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="57" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>74</v>
       </c>
@@ -3321,7 +3323,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="58" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="G58" t="s">
         <v>9</v>
       </c>
@@ -3329,34 +3331,34 @@
         <v>75</v>
       </c>
     </row>
-    <row r="59" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="2" t="s">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A59" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="B59" s="2">
+      <c r="B59" s="3">
         <v>1806</v>
       </c>
-      <c r="C59" s="2">
+      <c r="C59" s="3">
         <v>144</v>
       </c>
-      <c r="D59" s="2">
+      <c r="D59" s="3">
         <v>54</v>
       </c>
-      <c r="E59" s="2">
+      <c r="E59" s="3">
         <v>1</v>
       </c>
-      <c r="F59" s="2" t="str" cm="1">
+      <c r="F59" s="3" t="str" cm="1">
         <f t="array" ref="F59">IF(AND(NOT(ISBLANK(C59:E59)),OR(C59&gt;=200,(D59+E59)&gt;40)),"Yes","No")</f>
         <v>Yes</v>
       </c>
-      <c r="G59" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H59" s="3" t="s">
+      <c r="G59" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H59" s="4" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="60" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="G60" t="s">
         <v>9</v>
       </c>
@@ -3364,7 +3366,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="61" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="G61" t="s">
         <v>9</v>
       </c>
@@ -3372,7 +3374,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="62" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="G62" t="s">
         <v>9</v>
       </c>
@@ -3380,7 +3382,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="63" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>82</v>
       </c>
@@ -3407,7 +3409,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="64" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>83</v>
       </c>
@@ -3434,7 +3436,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="65" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>84</v>
       </c>
@@ -3462,33 +3464,33 @@
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A66" t="s">
+      <c r="A66" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="B66">
+      <c r="B66" s="3">
         <v>17</v>
       </c>
-      <c r="C66">
+      <c r="C66" s="3">
         <v>204</v>
       </c>
-      <c r="D66">
+      <c r="D66" s="3">
         <v>3</v>
       </c>
-      <c r="E66">
+      <c r="E66" s="3">
         <v>25</v>
       </c>
-      <c r="F66" t="str" cm="1">
+      <c r="F66" s="3" t="str" cm="1">
         <f t="array" ref="F66">IF(AND(NOT(ISBLANK(C66:E66)),OR(C66&gt;=200,(D66+E66)&gt;40)),"Yes","No")</f>
         <v>Yes</v>
       </c>
-      <c r="G66" t="s">
-        <v>20</v>
-      </c>
-      <c r="H66" s="1" t="s">
+      <c r="G66" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H66" s="4" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="67" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>88</v>
       </c>
@@ -3515,7 +3517,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="68" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="G68" t="s">
         <v>9</v>
       </c>
@@ -3523,7 +3525,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="69" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>91</v>
       </c>
@@ -3550,7 +3552,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="70" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>93</v>
       </c>
@@ -3577,7 +3579,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="71" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="G71" t="s">
         <v>9</v>
       </c>
@@ -3585,7 +3587,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="72" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>96</v>
       </c>
@@ -3612,7 +3614,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="73" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>97</v>
       </c>
@@ -3639,7 +3641,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="74" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>98</v>
       </c>
@@ -3666,7 +3668,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="75" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>99</v>
       </c>
@@ -3693,7 +3695,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="76" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>101</v>
       </c>
@@ -3720,7 +3722,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="77" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>103</v>
       </c>
@@ -3744,7 +3746,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="78" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="G78" t="s">
         <v>9</v>
       </c>
@@ -3752,7 +3754,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="79" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="G79" t="s">
         <v>9</v>
       </c>
@@ -3760,7 +3762,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="80" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="G80" t="s">
         <v>9</v>
       </c>
@@ -3768,7 +3770,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="81" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="G81" t="s">
         <v>9</v>
       </c>
@@ -3776,7 +3778,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="82" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>109</v>
       </c>
@@ -3803,7 +3805,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="83" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>110</v>
       </c>
@@ -3830,7 +3832,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="84" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>111</v>
       </c>
@@ -3857,7 +3859,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="85" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>112</v>
       </c>
@@ -3884,7 +3886,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="86" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>113</v>
       </c>
@@ -3911,7 +3913,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="87" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>114</v>
       </c>
@@ -3938,7 +3940,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="88" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>115</v>
       </c>
@@ -3965,7 +3967,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="89" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>116</v>
       </c>
@@ -3992,7 +3994,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="90" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="G90" t="s">
         <v>9</v>
       </c>
@@ -4000,7 +4002,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="91" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="G91" t="s">
         <v>9</v>
       </c>
@@ -4008,7 +4010,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="92" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>120</v>
       </c>
@@ -4035,7 +4037,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="93" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>121</v>
       </c>
@@ -4062,7 +4064,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="94" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>122</v>
       </c>
@@ -4089,7 +4091,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="95" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>43</v>
       </c>
@@ -4116,7 +4118,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="96" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="G96" t="s">
         <v>9</v>
       </c>
@@ -4124,7 +4126,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="97" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="G97" t="s">
         <v>9</v>
       </c>
@@ -4132,7 +4134,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="98" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="G98" t="s">
         <v>9</v>
       </c>
@@ -4140,7 +4142,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="99" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>127</v>
       </c>
@@ -4167,7 +4169,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="100" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="G100" t="s">
         <v>9</v>
       </c>
@@ -4175,7 +4177,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="101" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="G101" t="s">
         <v>9</v>
       </c>
@@ -4183,7 +4185,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="102" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>131</v>
       </c>
@@ -4210,7 +4212,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="103" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>132</v>
       </c>
@@ -4237,7 +4239,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="104" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>133</v>
       </c>
@@ -4265,33 +4267,33 @@
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A105" t="s">
+      <c r="A105" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="B105">
+      <c r="B105" s="3">
         <v>13</v>
       </c>
-      <c r="C105">
+      <c r="C105" s="3">
         <v>313</v>
       </c>
-      <c r="D105">
+      <c r="D105" s="3">
         <v>2</v>
       </c>
-      <c r="E105">
+      <c r="E105" s="3">
         <v>14</v>
       </c>
-      <c r="F105" t="str" cm="1">
+      <c r="F105" s="3" t="str" cm="1">
         <f t="array" ref="F105">IF(AND(NOT(ISBLANK(C105:E105)),OR(C105&gt;=200,(D105+E105)&gt;40)),"Yes","No")</f>
         <v>Yes</v>
       </c>
-      <c r="G105" t="s">
-        <v>20</v>
-      </c>
-      <c r="H105" s="1" t="s">
+      <c r="G105" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H105" s="4" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="106" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>136</v>
       </c>
@@ -4318,7 +4320,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="107" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>137</v>
       </c>
@@ -4345,7 +4347,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="108" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>138</v>
       </c>
@@ -4373,113 +4375,113 @@
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A109" t="s">
+      <c r="A109" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="B109">
+      <c r="B109" s="3">
         <v>1106</v>
       </c>
-      <c r="C109">
+      <c r="C109" s="3">
         <v>210</v>
       </c>
-      <c r="D109">
+      <c r="D109" s="3">
         <v>15</v>
       </c>
-      <c r="E109">
+      <c r="E109" s="3">
         <v>7</v>
       </c>
-      <c r="F109" t="str" cm="1">
+      <c r="F109" s="3" t="str" cm="1">
         <f t="array" ref="F109">IF(AND(NOT(ISBLANK(C109:E109)),OR(C109&gt;=200,(D109+E109)&gt;40)),"Yes","No")</f>
         <v>Yes</v>
       </c>
-      <c r="G109" t="s">
-        <v>20</v>
-      </c>
-      <c r="H109" s="1" t="s">
+      <c r="G109" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H109" s="4" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A110" t="s">
-        <v>140</v>
-      </c>
-      <c r="B110">
+      <c r="A110" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="B110" s="3">
         <v>1535</v>
       </c>
-      <c r="C110">
+      <c r="C110" s="3">
         <v>369</v>
       </c>
-      <c r="D110">
+      <c r="D110" s="3">
         <v>12</v>
       </c>
-      <c r="E110">
+      <c r="E110" s="3">
         <v>23</v>
       </c>
-      <c r="F110" t="str" cm="1">
+      <c r="F110" s="3" t="str" cm="1">
         <f t="array" ref="F110">IF(AND(NOT(ISBLANK(C110:E110)),OR(C110&gt;=200,(D110+E110)&gt;40)),"Yes","No")</f>
         <v>Yes</v>
       </c>
-      <c r="G110" t="s">
-        <v>20</v>
-      </c>
-      <c r="H110" s="1" t="s">
+      <c r="G110" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H110" s="4" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="111" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A111" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="B111" s="2">
+        <v>140</v>
+      </c>
+      <c r="B111" s="3">
         <v>2035</v>
       </c>
-      <c r="C111" s="2">
+      <c r="C111" s="3">
         <v>274</v>
       </c>
-      <c r="D111" s="2">
+      <c r="D111" s="3">
         <v>10</v>
       </c>
-      <c r="E111" s="2">
+      <c r="E111" s="3">
         <v>15</v>
       </c>
-      <c r="F111" s="2" t="str" cm="1">
+      <c r="F111" s="3" t="str" cm="1">
         <f t="array" ref="F111">IF(AND(NOT(ISBLANK(C111:E111)),OR(C111&gt;=200,(D111+E111)&gt;40)),"Yes","No")</f>
         <v>Yes</v>
       </c>
-      <c r="G111" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H111" s="3" t="s">
+      <c r="G111" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H111" s="4" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="112" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="G112" t="s">
         <v>9</v>
       </c>
       <c r="H112" s="1" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+      <c r="G113" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H113" s="1" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="113" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
-      <c r="G113" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H113" s="1" t="s">
+    <row r="114" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+      <c r="G114" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H114" s="1" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="114" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
-      <c r="G114" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H114" s="1" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="115" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B115">
         <v>64</v>
@@ -4501,39 +4503,39 @@
         <v>20</v>
       </c>
       <c r="H115" s="1" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="116" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.2">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A116" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="B116" s="2">
+        <v>146</v>
+      </c>
+      <c r="B116" s="3">
         <v>99</v>
       </c>
-      <c r="C116" s="2">
+      <c r="C116" s="3">
         <v>135</v>
       </c>
-      <c r="D116" s="2">
+      <c r="D116" s="3">
         <v>46</v>
       </c>
-      <c r="E116" s="2">
+      <c r="E116" s="3">
         <v>2</v>
       </c>
-      <c r="F116" s="2" t="str" cm="1">
+      <c r="F116" s="3" t="str" cm="1">
         <f t="array" ref="F116">IF(AND(NOT(ISBLANK(C116:E116)),OR(C116&gt;=200,(D116+E116)&gt;40)),"Yes","No")</f>
         <v>Yes</v>
       </c>
-      <c r="G116" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="H116" s="3" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="117" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+      <c r="G116" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H116" s="4" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B117">
         <v>294</v>
@@ -4555,12 +4557,12 @@
         <v>20</v>
       </c>
       <c r="H117" s="1" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="118" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B118">
         <v>352</v>
@@ -4582,12 +4584,12 @@
         <v>20</v>
       </c>
       <c r="H118" s="1" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="119" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B119">
         <v>398</v>
@@ -4609,12 +4611,12 @@
         <v>20</v>
       </c>
       <c r="H119" s="1" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="120" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B120">
         <v>472</v>
@@ -4636,20 +4638,20 @@
         <v>20</v>
       </c>
       <c r="H120" s="1" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="121" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="G121" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H121" s="1" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="122" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B122">
         <v>17</v>
@@ -4671,20 +4673,20 @@
         <v>20</v>
       </c>
       <c r="H122" s="1" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="123" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="G123" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H123" s="1" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="124" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B124">
         <v>10</v>
@@ -4706,12 +4708,12 @@
         <v>20</v>
       </c>
       <c r="H124" s="1" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="125" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B125">
         <v>38</v>
@@ -4733,12 +4735,12 @@
         <v>20</v>
       </c>
       <c r="H125" s="1" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="126" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B126">
         <v>48</v>
@@ -4760,12 +4762,12 @@
         <v>20</v>
       </c>
       <c r="H126" s="1" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="127" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B127">
         <v>79</v>
@@ -4787,12 +4789,12 @@
         <v>20</v>
       </c>
       <c r="H127" s="1" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="128" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B128">
         <v>101</v>
@@ -4814,28 +4816,28 @@
         <v>20</v>
       </c>
       <c r="H128" s="1" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="129" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="G129" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H129" s="1" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+      <c r="G130" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H130" s="1" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="130" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
-      <c r="G130" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H130" s="1" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="131" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B131">
         <v>19</v>
@@ -4857,12 +4859,12 @@
         <v>20</v>
       </c>
       <c r="H131" s="1" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="132" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B132">
         <v>49</v>
@@ -4884,12 +4886,12 @@
         <v>20</v>
       </c>
       <c r="H132" s="1" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="133" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B133">
         <v>50</v>
@@ -4911,39 +4913,39 @@
         <v>20</v>
       </c>
       <c r="H133" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A134" t="s">
-        <v>170</v>
-      </c>
-      <c r="B134">
+      <c r="A134" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="B134" s="3">
         <v>726</v>
       </c>
-      <c r="C134">
+      <c r="C134" s="3">
         <v>703</v>
       </c>
-      <c r="D134">
+      <c r="D134" s="3">
         <v>38</v>
       </c>
-      <c r="E134">
+      <c r="E134" s="3">
         <v>26</v>
       </c>
-      <c r="F134" t="str" cm="1">
+      <c r="F134" s="3" t="str" cm="1">
         <f t="array" ref="F134">IF(AND(NOT(ISBLANK(C134:E134)),OR(C134&gt;=200,(D134+E134)&gt;40)),"Yes","No")</f>
         <v>Yes</v>
       </c>
-      <c r="G134" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H134" s="1" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="135" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+      <c r="G134" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H134" s="4" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B135">
         <v>39</v>
@@ -4965,12 +4967,12 @@
         <v>20</v>
       </c>
       <c r="H135" s="1" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A136" t="s">
         <v>171</v>
-      </c>
-    </row>
-    <row r="136" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A136" t="s">
-        <v>172</v>
       </c>
       <c r="B136">
         <v>39</v>
@@ -4992,12 +4994,12 @@
         <v>20</v>
       </c>
       <c r="H136" s="1" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="137" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B137">
         <v>12</v>
@@ -5019,12 +5021,12 @@
         <v>20</v>
       </c>
       <c r="H137" s="1" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="138" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B138">
         <v>23</v>
@@ -5046,12 +5048,12 @@
         <v>20</v>
       </c>
       <c r="H138" s="1" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="139" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B139">
         <v>76</v>
@@ -5073,12 +5075,12 @@
         <v>20</v>
       </c>
       <c r="H139" s="1" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="140" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B140">
         <v>148</v>
@@ -5100,12 +5102,12 @@
         <v>20</v>
       </c>
       <c r="H140" s="1" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="141" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B141">
         <v>6</v>
@@ -5127,12 +5129,12 @@
         <v>20</v>
       </c>
       <c r="H141" s="1" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="142" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B142">
         <v>3</v>
@@ -5154,20 +5156,20 @@
         <v>20</v>
       </c>
       <c r="H142" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="143" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="G143" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H143" s="1" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="144" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B144">
         <v>503</v>
@@ -5189,12 +5191,12 @@
         <v>20</v>
       </c>
       <c r="H144" s="1" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="145" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B145">
         <v>507</v>
@@ -5216,12 +5218,12 @@
         <v>20</v>
       </c>
       <c r="H145" s="1" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="146" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B146">
         <v>513</v>
@@ -5243,12 +5245,12 @@
         <v>20</v>
       </c>
       <c r="H146" s="1" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="147" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B147">
         <v>521</v>
@@ -5270,12 +5272,12 @@
         <v>20</v>
       </c>
       <c r="H147" s="1" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="148" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B148">
         <v>528</v>
@@ -5297,12 +5299,12 @@
         <v>20</v>
       </c>
       <c r="H148" s="1" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="149" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B149">
         <v>536</v>
@@ -5324,12 +5326,12 @@
         <v>20</v>
       </c>
       <c r="H149" s="1" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="150" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B150">
         <v>544</v>
@@ -5351,12 +5353,12 @@
         <v>20</v>
       </c>
       <c r="H150" s="1" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="151" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B151">
         <v>551</v>
@@ -5378,12 +5380,12 @@
         <v>20</v>
       </c>
       <c r="H151" s="1" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="152" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B152">
         <v>558</v>
@@ -5405,12 +5407,12 @@
         <v>20</v>
       </c>
       <c r="H152" s="1" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="153" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="153" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B153">
         <v>565</v>
@@ -5432,12 +5434,12 @@
         <v>20</v>
       </c>
       <c r="H153" s="1" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="154" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="154" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B154">
         <v>572</v>
@@ -5459,12 +5461,12 @@
         <v>20</v>
       </c>
       <c r="H154" s="1" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="155" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="155" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B155">
         <v>580</v>
@@ -5486,12 +5488,12 @@
         <v>20</v>
       </c>
       <c r="H155" s="1" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="156" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="156" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B156">
         <v>588</v>
@@ -5513,12 +5515,12 @@
         <v>20</v>
       </c>
       <c r="H156" s="1" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="157" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="157" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B157">
         <v>596</v>
@@ -5540,12 +5542,12 @@
         <v>20</v>
       </c>
       <c r="H157" s="1" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="158" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="158" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B158">
         <v>602</v>
@@ -5567,12 +5569,12 @@
         <v>20</v>
       </c>
       <c r="H158" s="1" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="159" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="159" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B159">
         <v>606</v>
@@ -5594,39 +5596,39 @@
         <v>20</v>
       </c>
       <c r="H159" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A160" t="s">
-        <v>201</v>
-      </c>
-      <c r="B160">
+      <c r="A160" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="B160" s="3">
         <v>614</v>
       </c>
-      <c r="C160">
+      <c r="C160" s="3">
         <v>271</v>
       </c>
-      <c r="D160">
+      <c r="D160" s="3">
         <v>22</v>
       </c>
-      <c r="E160">
+      <c r="E160" s="3">
         <v>11</v>
       </c>
-      <c r="F160" t="str" cm="1">
+      <c r="F160" s="3" t="str" cm="1">
         <f t="array" ref="F160">IF(AND(NOT(ISBLANK(C160:E160)),OR(C160&gt;=200,(D160+E160)&gt;40)),"Yes","No")</f>
         <v>Yes</v>
       </c>
-      <c r="G160" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H160" s="1" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="161" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+      <c r="G160" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H160" s="4" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="161" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B161">
         <v>994</v>
@@ -5648,12 +5650,12 @@
         <v>20</v>
       </c>
       <c r="H161" s="1" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="162" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="162" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B162">
         <v>1008</v>
@@ -5675,12 +5677,12 @@
         <v>20</v>
       </c>
       <c r="H162" s="1" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="163" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="163" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B163">
         <v>1055</v>
@@ -5702,12 +5704,12 @@
         <v>20</v>
       </c>
       <c r="H163" s="1" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="164" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="164" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B164">
         <v>1067</v>
@@ -5729,12 +5731,12 @@
         <v>20</v>
       </c>
       <c r="H164" s="1" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="165" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="165" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B165">
         <v>1079</v>
@@ -5756,12 +5758,12 @@
         <v>20</v>
       </c>
       <c r="H165" s="1" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="166" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="166" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B166">
         <v>1088</v>
@@ -5783,12 +5785,12 @@
         <v>20</v>
       </c>
       <c r="H166" s="1" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="167" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="167" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B167">
         <v>1097</v>
@@ -5810,12 +5812,12 @@
         <v>20</v>
       </c>
       <c r="H167" s="1" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="168" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="168" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B168">
         <v>1106</v>
@@ -5837,12 +5839,12 @@
         <v>20</v>
       </c>
       <c r="H168" s="1" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="169" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="169" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A169" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B169">
         <v>1115</v>
@@ -5864,12 +5866,12 @@
         <v>20</v>
       </c>
       <c r="H169" s="1" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="170" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="170" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A170" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B170">
         <v>1124</v>
@@ -5891,12 +5893,12 @@
         <v>20</v>
       </c>
       <c r="H170" s="1" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="171" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="171" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A171" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B171">
         <v>1160</v>
@@ -5918,12 +5920,12 @@
         <v>20</v>
       </c>
       <c r="H171" s="1" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="172" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="172" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A172" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B172">
         <v>1229</v>
@@ -5945,12 +5947,12 @@
         <v>20</v>
       </c>
       <c r="H172" s="1" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="173" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="173" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A173" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B173">
         <v>1233</v>
@@ -5972,12 +5974,12 @@
         <v>20</v>
       </c>
       <c r="H173" s="1" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="174" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="174" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A174" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B174">
         <v>1237</v>
@@ -5999,12 +6001,12 @@
         <v>20</v>
       </c>
       <c r="H174" s="1" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="175" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="175" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A175" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B175">
         <v>1348</v>
@@ -6026,12 +6028,12 @@
         <v>20</v>
       </c>
       <c r="H175" s="1" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="176" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="176" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A176" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B176">
         <v>1377</v>
@@ -6053,12 +6055,12 @@
         <v>20</v>
       </c>
       <c r="H176" s="1" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="177" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="177" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A177" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B177">
         <v>1382</v>
@@ -6080,12 +6082,12 @@
         <v>20</v>
       </c>
       <c r="H177" s="1" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="178" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="178" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A178" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B178">
         <v>1387</v>
@@ -6107,12 +6109,12 @@
         <v>20</v>
       </c>
       <c r="H178" s="1" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="179" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="179" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A179" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B179">
         <v>1391</v>
@@ -6134,12 +6136,12 @@
         <v>20</v>
       </c>
       <c r="H179" s="1" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="180" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="180" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A180" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B180">
         <v>1395</v>
@@ -6161,12 +6163,12 @@
         <v>20</v>
       </c>
       <c r="H180" s="1" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="181" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="181" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A181" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B181">
         <v>1401</v>
@@ -6188,12 +6190,12 @@
         <v>20</v>
       </c>
       <c r="H181" s="1" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="182" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="182" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A182" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B182">
         <v>1430</v>
@@ -6215,12 +6217,12 @@
         <v>20</v>
       </c>
       <c r="H182" s="1" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="183" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="183" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A183" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B183">
         <v>1437</v>
@@ -6242,12 +6244,12 @@
         <v>20</v>
       </c>
       <c r="H183" s="1" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="184" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="184" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A184" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B184">
         <v>1442</v>
@@ -6269,12 +6271,12 @@
         <v>20</v>
       </c>
       <c r="H184" s="1" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="185" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="185" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A185" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B185">
         <v>1446</v>
@@ -6296,12 +6298,12 @@
         <v>20</v>
       </c>
       <c r="H185" s="1" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="186" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="186" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A186" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B186">
         <v>1450</v>
@@ -6323,12 +6325,12 @@
         <v>20</v>
       </c>
       <c r="H186" s="1" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="187" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="187" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A187" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B187">
         <v>1468</v>
@@ -6350,12 +6352,12 @@
         <v>20</v>
       </c>
       <c r="H187" s="1" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="188" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="188" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A188" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B188">
         <v>1669</v>
@@ -6377,12 +6379,12 @@
         <v>20</v>
       </c>
       <c r="H188" s="1" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="189" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="189" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A189" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B189">
         <v>1799</v>
@@ -6404,12 +6406,12 @@
         <v>20</v>
       </c>
       <c r="H189" s="1" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="190" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="190" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A190" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B190">
         <v>1817</v>
@@ -6431,12 +6433,12 @@
         <v>20</v>
       </c>
       <c r="H190" s="1" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="191" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="191" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A191" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B191">
         <v>1830</v>
@@ -6458,12 +6460,12 @@
         <v>20</v>
       </c>
       <c r="H191" s="1" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="192" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="192" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A192" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B192">
         <v>1836</v>
@@ -6485,12 +6487,12 @@
         <v>20</v>
       </c>
       <c r="H192" s="1" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="193" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="193" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A193" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B193">
         <v>1841</v>
@@ -6512,12 +6514,12 @@
         <v>20</v>
       </c>
       <c r="H193" s="1" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="194" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="194" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A194" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B194">
         <v>1942</v>
@@ -6539,12 +6541,12 @@
         <v>20</v>
       </c>
       <c r="H194" s="1" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="195" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="195" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A195" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B195">
         <v>1955</v>
@@ -6566,12 +6568,12 @@
         <v>20</v>
       </c>
       <c r="H195" s="1" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="196" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="196" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A196" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B196">
         <v>1960</v>
@@ -6593,12 +6595,12 @@
         <v>20</v>
       </c>
       <c r="H196" s="1" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="197" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="197" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A197" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B197">
         <v>1965</v>
@@ -6620,12 +6622,12 @@
         <v>20</v>
       </c>
       <c r="H197" s="1" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="198" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="198" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A198" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B198">
         <v>2060</v>
@@ -6647,12 +6649,12 @@
         <v>20</v>
       </c>
       <c r="H198" s="1" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="199" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="199" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A199" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B199">
         <v>2292</v>
@@ -6674,12 +6676,12 @@
         <v>20</v>
       </c>
       <c r="H199" s="1" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="200" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="200" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A200" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B200">
         <v>2209</v>
@@ -6701,12 +6703,12 @@
         <v>20</v>
       </c>
       <c r="H200" s="1" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="201" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="201" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A201" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B201">
         <v>2212</v>
@@ -6728,12 +6730,12 @@
         <v>20</v>
       </c>
       <c r="H201" s="1" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="202" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="202" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A202" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B202">
         <v>2225</v>
@@ -6755,12 +6757,12 @@
         <v>20</v>
       </c>
       <c r="H202" s="1" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="203" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="203" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A203" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B203">
         <v>2234</v>
@@ -6782,12 +6784,12 @@
         <v>20</v>
       </c>
       <c r="H203" s="1" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="204" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="204" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A204" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B204">
         <v>2242</v>
@@ -6809,12 +6811,12 @@
         <v>20</v>
       </c>
       <c r="H204" s="1" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="205" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="205" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A205" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B205">
         <v>2245</v>
@@ -6836,12 +6838,12 @@
         <v>20</v>
       </c>
       <c r="H205" s="1" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="206" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="206" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A206" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B206">
         <v>2268</v>
@@ -6863,12 +6865,12 @@
         <v>20</v>
       </c>
       <c r="H206" s="1" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="207" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="207" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A207" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B207">
         <v>2344</v>
@@ -6890,12 +6892,12 @@
         <v>20</v>
       </c>
       <c r="H207" s="1" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="208" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="208" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A208" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B208">
         <v>2398</v>
@@ -6917,12 +6919,12 @@
         <v>20</v>
       </c>
       <c r="H208" s="1" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="209" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="209" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A209" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B209">
         <v>2450</v>
@@ -6944,12 +6946,12 @@
         <v>20</v>
       </c>
       <c r="H209" s="1" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="210" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="210" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A210" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B210">
         <v>2480</v>
@@ -6971,12 +6973,12 @@
         <v>20</v>
       </c>
       <c r="H210" s="1" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="211" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="211" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A211" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B211">
         <v>2550</v>
@@ -6998,12 +7000,12 @@
         <v>20</v>
       </c>
       <c r="H211" s="1" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="212" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="212" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A212" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B212">
         <v>2555</v>
@@ -7025,12 +7027,12 @@
         <v>20</v>
       </c>
       <c r="H212" s="1" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="213" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="213" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A213" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B213">
         <v>2560</v>
@@ -7052,12 +7054,12 @@
         <v>20</v>
       </c>
       <c r="H213" s="1" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="214" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="214" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A214" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B214">
         <v>2565</v>
@@ -7079,12 +7081,12 @@
         <v>20</v>
       </c>
       <c r="H214" s="1" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="215" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="215" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A215" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B215">
         <v>2602</v>
@@ -7106,12 +7108,12 @@
         <v>20</v>
       </c>
       <c r="H215" s="1" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="216" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="216" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A216" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B216">
         <v>2614</v>
@@ -7133,12 +7135,12 @@
         <v>20</v>
       </c>
       <c r="H216" s="1" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="217" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="217" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A217" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B217">
         <v>2653</v>
@@ -7160,12 +7162,12 @@
         <v>20</v>
       </c>
       <c r="H217" s="1" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="218" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="218" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A218" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B218">
         <v>2695</v>
@@ -7187,12 +7189,12 @@
         <v>20</v>
       </c>
       <c r="H218" s="1" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="219" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="219" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A219" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B219">
         <v>2784</v>
@@ -7214,12 +7216,12 @@
         <v>20</v>
       </c>
       <c r="H219" s="1" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="220" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="220" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A220" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B220">
         <v>2795</v>
@@ -7241,12 +7243,12 @@
         <v>20</v>
       </c>
       <c r="H220" s="1" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="221" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="221" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A221" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B221">
         <v>2801</v>
@@ -7268,12 +7270,12 @@
         <v>20</v>
       </c>
       <c r="H221" s="1" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="222" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="222" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A222" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B222">
         <v>2807</v>
@@ -7295,12 +7297,12 @@
         <v>20</v>
       </c>
       <c r="H222" s="1" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="223" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="223" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A223" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B223">
         <v>2813</v>
@@ -7322,12 +7324,12 @@
         <v>20</v>
       </c>
       <c r="H223" s="1" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="224" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="224" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A224" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B224">
         <v>2819</v>
@@ -7349,12 +7351,12 @@
         <v>20</v>
       </c>
       <c r="H224" s="1" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="225" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="225" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A225" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B225">
         <v>2825</v>
@@ -7376,12 +7378,12 @@
         <v>20</v>
       </c>
       <c r="H225" s="1" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="226" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="226" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A226" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B226">
         <v>2831</v>
@@ -7403,12 +7405,12 @@
         <v>20</v>
       </c>
       <c r="H226" s="1" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="227" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="227" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A227" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B227">
         <v>2837</v>
@@ -7430,12 +7432,12 @@
         <v>20</v>
       </c>
       <c r="H227" s="1" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="228" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="228" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A228" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B228">
         <v>2843</v>
@@ -7457,12 +7459,12 @@
         <v>20</v>
       </c>
       <c r="H228" s="1" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="229" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="229" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A229" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B229">
         <v>2849</v>
@@ -7484,12 +7486,12 @@
         <v>20</v>
       </c>
       <c r="H229" s="1" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="230" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="230" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A230" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B230">
         <v>2880</v>
@@ -7511,36 +7513,36 @@
         <v>20</v>
       </c>
       <c r="H230" s="1" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="231" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="231" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="G231" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H231" s="1" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="232" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+      <c r="G232" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H232" s="1" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="232" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
-      <c r="G232" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H232" s="1" t="s">
+    <row r="233" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+      <c r="G233" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H233" s="1" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="233" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
-      <c r="G233" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H233" s="1" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="234" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A234" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B234">
         <v>8</v>
@@ -7562,66 +7564,66 @@
         <v>20</v>
       </c>
       <c r="H234" s="1" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="235" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.2">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="235" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A235" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="B235" s="2">
+        <v>277</v>
+      </c>
+      <c r="B235" s="3">
         <v>26</v>
       </c>
-      <c r="C235" s="2">
+      <c r="C235" s="3">
         <v>304</v>
       </c>
-      <c r="D235" s="2">
+      <c r="D235" s="3">
         <v>8</v>
       </c>
-      <c r="E235" s="2">
+      <c r="E235" s="3">
         <v>27</v>
       </c>
-      <c r="F235" s="2" t="str" cm="1">
+      <c r="F235" s="3" t="str" cm="1">
         <f t="array" ref="F235">IF(AND(NOT(ISBLANK(C235:E235)),OR(C235&gt;=200,(D235+E235)&gt;40)),"Yes","No")</f>
         <v>Yes</v>
       </c>
-      <c r="G235" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="H235" s="3" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="236" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="G235" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H235" s="4" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="236" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A236" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="B236" s="2">
+        <v>279</v>
+      </c>
+      <c r="B236" s="3">
         <v>25</v>
       </c>
-      <c r="C236" s="2">
+      <c r="C236" s="3">
         <v>521</v>
       </c>
-      <c r="D236" s="2">
+      <c r="D236" s="3">
         <v>10</v>
       </c>
-      <c r="E236" s="2">
+      <c r="E236" s="3">
         <v>25</v>
       </c>
-      <c r="F236" s="2" t="str" cm="1">
+      <c r="F236" s="3" t="str" cm="1">
         <f t="array" ref="F236">IF(AND(NOT(ISBLANK(C236:E236)),OR(C236&gt;=200,(D236+E236)&gt;40)),"Yes","No")</f>
         <v>Yes</v>
       </c>
-      <c r="G236" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="H236" s="3" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="237" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+      <c r="G236" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H236" s="4" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="237" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A237" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B237">
         <v>4</v>
@@ -7643,12 +7645,12 @@
         <v>20</v>
       </c>
       <c r="H237" s="1" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="238" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="238" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A238" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B238">
         <v>8</v>
@@ -7670,39 +7672,39 @@
         <v>20</v>
       </c>
       <c r="H238" s="1" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="239" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.2">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="239" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A239" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="B239" s="2">
+        <v>285</v>
+      </c>
+      <c r="B239" s="3">
         <v>38</v>
       </c>
-      <c r="C239" s="2">
+      <c r="C239" s="3">
         <v>571</v>
       </c>
-      <c r="D239" s="2">
+      <c r="D239" s="3">
         <v>19</v>
       </c>
-      <c r="E239" s="2">
+      <c r="E239" s="3">
         <v>24</v>
       </c>
-      <c r="F239" s="2" t="str" cm="1">
+      <c r="F239" s="3" t="str" cm="1">
         <f t="array" ref="F239">IF(AND(NOT(ISBLANK(C239:E239)),OR(C239&gt;=200,(D239+E239)&gt;40)),"Yes","No")</f>
         <v>Yes</v>
       </c>
-      <c r="G239" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="H239" s="3" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="240" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+      <c r="G239" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H239" s="4" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="240" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A240" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B240">
         <v>7</v>
@@ -7724,12 +7726,12 @@
         <v>20</v>
       </c>
       <c r="H240" s="1" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="241" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="241" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A241" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B241">
         <v>18</v>
@@ -7751,12 +7753,12 @@
         <v>20</v>
       </c>
       <c r="H241" s="1" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="242" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="242" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A242" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B242">
         <v>86</v>
@@ -7778,39 +7780,39 @@
         <v>20</v>
       </c>
       <c r="H242" s="1" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="243" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.2">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="243" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A243" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="B243" s="2">
+        <v>292</v>
+      </c>
+      <c r="B243" s="3">
         <v>30</v>
       </c>
-      <c r="C243" s="2">
+      <c r="C243" s="3">
         <v>355</v>
       </c>
-      <c r="D243" s="2">
+      <c r="D243" s="3">
         <v>19</v>
       </c>
-      <c r="E243" s="2">
+      <c r="E243" s="3">
         <v>5</v>
       </c>
-      <c r="F243" s="2" t="str" cm="1">
+      <c r="F243" s="3" t="str" cm="1">
         <f t="array" ref="F243">IF(AND(NOT(ISBLANK(C243:E243)),OR(C243&gt;=200,(D243+E243)&gt;40)),"Yes","No")</f>
         <v>Yes</v>
       </c>
-      <c r="G243" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="H243" s="3" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="244" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+      <c r="G243" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H243" s="4" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="244" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A244" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B244">
         <v>495</v>
@@ -7832,12 +7834,12 @@
         <v>20</v>
       </c>
       <c r="H244" s="1" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="245" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="245" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A245" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B245">
         <v>8</v>
@@ -7859,12 +7861,12 @@
         <v>20</v>
       </c>
       <c r="H245" s="1" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="246" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="246" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A246" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B246">
         <v>5</v>
@@ -7886,12 +7888,12 @@
         <v>20</v>
       </c>
       <c r="H246" s="1" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="247" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="247" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A247" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B247">
         <v>6</v>
@@ -7913,12 +7915,12 @@
         <v>20</v>
       </c>
       <c r="H247" s="1" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="248" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="248" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A248" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B248">
         <v>9</v>
@@ -7940,12 +7942,12 @@
         <v>20</v>
       </c>
       <c r="H248" s="1" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="249" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="249" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A249" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B249">
         <v>4</v>
@@ -7967,12 +7969,12 @@
         <v>20</v>
       </c>
       <c r="H249" s="1" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="250" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="250" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A250" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B250">
         <v>12</v>
@@ -7994,12 +7996,12 @@
         <v>20</v>
       </c>
       <c r="H250" s="1" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="251" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="251" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A251" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B251">
         <v>9</v>
@@ -8021,12 +8023,12 @@
         <v>20</v>
       </c>
       <c r="H251" s="1" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="252" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="252" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A252" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B252">
         <v>42</v>
@@ -8048,39 +8050,39 @@
         <v>20</v>
       </c>
       <c r="H252" s="1" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="253" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.2">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="253" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A253" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="B253" s="2">
+        <v>310</v>
+      </c>
+      <c r="B253" s="3">
         <v>59</v>
       </c>
-      <c r="C253" s="2">
+      <c r="C253" s="3">
         <v>451</v>
       </c>
-      <c r="D253" s="2">
+      <c r="D253" s="3">
         <v>34</v>
       </c>
-      <c r="E253" s="2">
+      <c r="E253" s="3">
         <v>29</v>
       </c>
-      <c r="F253" s="2" t="str" cm="1">
+      <c r="F253" s="3" t="str" cm="1">
         <f t="array" ref="F253">IF(AND(NOT(ISBLANK(C253:E253)),OR(C253&gt;=200,(D253+E253)&gt;40)),"Yes","No")</f>
         <v>Yes</v>
       </c>
-      <c r="G253" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="H253" s="3" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="254" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+      <c r="G253" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H253" s="4" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="254" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A254" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B254">
         <v>16</v>
@@ -8102,12 +8104,12 @@
         <v>20</v>
       </c>
       <c r="H254" s="1" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="255" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="255" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A255" s="1" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B255">
         <v>16</v>
@@ -8129,12 +8131,12 @@
         <v>20</v>
       </c>
       <c r="H255" s="1" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="256" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="256" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A256" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B256">
         <v>54</v>
@@ -8156,12 +8158,12 @@
         <v>20</v>
       </c>
       <c r="H256" s="1" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="257" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="257" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A257" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B257">
         <v>6</v>
@@ -8183,12 +8185,12 @@
         <v>20</v>
       </c>
       <c r="H257" s="1" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="258" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="258" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A258" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B258">
         <v>6</v>
@@ -8210,12 +8212,12 @@
         <v>20</v>
       </c>
       <c r="H258" s="1" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="259" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="259" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A259" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B259">
         <v>33</v>
@@ -8237,12 +8239,12 @@
         <v>20</v>
       </c>
       <c r="H259" s="1" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="260" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="260" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A260" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B260">
         <v>272</v>
@@ -8264,12 +8266,12 @@
         <v>20</v>
       </c>
       <c r="H260" s="1" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="261" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="261" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A261" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B261">
         <v>5</v>
@@ -8291,12 +8293,12 @@
         <v>20</v>
       </c>
       <c r="H261" s="1" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="262" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="262" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A262" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B262">
         <v>13</v>
@@ -8318,12 +8320,12 @@
         <v>20</v>
       </c>
       <c r="H262" s="1" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="263" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="263" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A263" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B263">
         <v>17</v>
@@ -8345,12 +8347,12 @@
         <v>20</v>
       </c>
       <c r="H263" s="1" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="264" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="264" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A264" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B264">
         <v>30</v>
@@ -8372,12 +8374,12 @@
         <v>20</v>
       </c>
       <c r="H264" s="1" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="265" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="265" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A265" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B265">
         <v>83</v>
@@ -8399,12 +8401,12 @@
         <v>20</v>
       </c>
       <c r="H265" s="1" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="266" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="266" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A266" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B266">
         <v>103</v>
@@ -8426,12 +8428,12 @@
         <v>20</v>
       </c>
       <c r="H266" s="1" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="267" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="267" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A267" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B267">
         <v>137</v>
@@ -8453,12 +8455,12 @@
         <v>20</v>
       </c>
       <c r="H267" s="1" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="268" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="268" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A268" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B268">
         <v>186</v>
@@ -8480,12 +8482,12 @@
         <v>20</v>
       </c>
       <c r="H268" s="1" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="269" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="269" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A269" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B269">
         <v>206</v>
@@ -8507,12 +8509,12 @@
         <v>20</v>
       </c>
       <c r="H269" s="1" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="270" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="270" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A270" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B270">
         <v>7</v>
@@ -8534,12 +8536,12 @@
         <v>20</v>
       </c>
       <c r="H270" s="1" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="271" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="271" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A271" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B271">
         <v>6</v>
@@ -8561,12 +8563,12 @@
         <v>20</v>
       </c>
       <c r="H271" s="1" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="272" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="272" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A272" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B272">
         <v>7</v>
@@ -8588,12 +8590,12 @@
         <v>20</v>
       </c>
       <c r="H272" s="1" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="273" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="273" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A273" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B273">
         <v>24</v>
@@ -8615,12 +8617,12 @@
         <v>20</v>
       </c>
       <c r="H273" s="1" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="274" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="274" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A274" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B274">
         <v>52</v>
@@ -8642,12 +8644,12 @@
         <v>20</v>
       </c>
       <c r="H274" s="1" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="275" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="275" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A275" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B275">
         <v>6</v>
@@ -8669,12 +8671,12 @@
         <v>20</v>
       </c>
       <c r="H275" s="1" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="276" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="276" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A276" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B276">
         <v>5</v>
@@ -8696,12 +8698,12 @@
         <v>20</v>
       </c>
       <c r="H276" s="1" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="277" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="277" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A277" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B277">
         <v>11</v>
@@ -8723,12 +8725,12 @@
         <v>20</v>
       </c>
       <c r="H277" s="1" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="278" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="278" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A278" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B278">
         <v>67</v>
@@ -8750,12 +8752,12 @@
         <v>20</v>
       </c>
       <c r="H278" s="1" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="279" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="279" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A279" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B279">
         <v>6</v>
@@ -8777,12 +8779,12 @@
         <v>20</v>
       </c>
       <c r="H279" s="1" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="280" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="280" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A280" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B280">
         <v>7</v>
@@ -8804,156 +8806,156 @@
         <v>20</v>
       </c>
       <c r="H280" s="1" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="281" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="281" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="G281" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H281" s="1" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="282" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+      <c r="G282" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H282" s="1" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="282" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
-      <c r="G282" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H282" s="1" t="s">
+    <row r="283" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+      <c r="G283" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H283" s="1" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="283" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
-      <c r="G283" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H283" s="1" t="s">
+    <row r="284" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+      <c r="G284" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H284" s="1" t="s">
         <v>357</v>
       </c>
     </row>
-    <row r="284" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
-      <c r="G284" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H284" s="1" t="s">
+    <row r="285" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+      <c r="G285" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H285" s="1" t="s">
         <v>358</v>
       </c>
     </row>
-    <row r="285" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
-      <c r="G285" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H285" s="1" t="s">
+    <row r="286" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+      <c r="G286" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H286" s="1" t="s">
         <v>359</v>
       </c>
     </row>
-    <row r="286" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
-      <c r="G286" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H286" s="1" t="s">
+    <row r="287" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+      <c r="G287" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H287" s="1" t="s">
         <v>360</v>
       </c>
     </row>
-    <row r="287" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
-      <c r="G287" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H287" s="1" t="s">
+    <row r="288" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+      <c r="G288" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H288" s="1" t="s">
         <v>361</v>
       </c>
     </row>
-    <row r="288" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
-      <c r="G288" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H288" s="1" t="s">
+    <row r="289" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+      <c r="G289" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H289" s="1" t="s">
         <v>362</v>
       </c>
     </row>
-    <row r="289" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
-      <c r="G289" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H289" s="1" t="s">
+    <row r="290" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+      <c r="G290" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H290" s="1" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="290" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
-      <c r="G290" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H290" s="1" t="s">
+    <row r="291" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+      <c r="G291" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H291" s="1" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="291" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
-      <c r="G291" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H291" s="1" t="s">
+    <row r="292" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+      <c r="G292" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H292" s="1" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="292" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
-      <c r="G292" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H292" s="1" t="s">
+    <row r="293" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+      <c r="G293" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H293" s="1" t="s">
         <v>366</v>
       </c>
     </row>
-    <row r="293" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
-      <c r="G293" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H293" s="1" t="s">
+    <row r="294" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+      <c r="G294" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H294" s="1" t="s">
         <v>367</v>
       </c>
     </row>
-    <row r="294" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
-      <c r="G294" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H294" s="1" t="s">
+    <row r="295" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+      <c r="G295" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H295" s="1" t="s">
         <v>368</v>
       </c>
     </row>
-    <row r="295" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
-      <c r="G295" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H295" s="1" t="s">
+    <row r="296" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+      <c r="G296" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H296" s="1" t="s">
         <v>369</v>
       </c>
     </row>
-    <row r="296" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
-      <c r="G296" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H296" s="1" t="s">
+    <row r="297" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+      <c r="G297" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H297" s="1" t="s">
         <v>370</v>
       </c>
     </row>
-    <row r="297" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
-      <c r="G297" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H297" s="1" t="s">
+    <row r="298" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+      <c r="G298" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H298" s="1" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="298" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
-      <c r="G298" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H298" s="1" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="299" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A299" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B299">
         <v>549</v>
@@ -8975,12 +8977,12 @@
         <v>20</v>
       </c>
       <c r="H299" s="1" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="300" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="300" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A300" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B300">
         <v>553</v>
@@ -9002,124 +9004,124 @@
         <v>20</v>
       </c>
       <c r="H300" s="1" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="301" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="301" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="G301" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H301" s="1" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="302" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+      <c r="G302" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H302" s="1" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="302" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
-      <c r="G302" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H302" s="1" t="s">
+    <row r="303" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+      <c r="G303" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H303" s="1" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="303" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
-      <c r="G303" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H303" s="1" t="s">
+    <row r="304" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+      <c r="G304" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H304" s="1" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="304" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
-      <c r="G304" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H304" s="1" t="s">
+    <row r="305" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+      <c r="G305" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H305" s="1" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="305" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
-      <c r="G305" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H305" s="1" t="s">
+    <row r="306" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+      <c r="G306" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H306" s="1" t="s">
         <v>380</v>
       </c>
     </row>
-    <row r="306" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
-      <c r="G306" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H306" s="1" t="s">
+    <row r="307" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+      <c r="G307" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H307" s="1" t="s">
         <v>381</v>
       </c>
     </row>
-    <row r="307" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
-      <c r="G307" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H307" s="1" t="s">
+    <row r="308" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+      <c r="G308" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H308" s="1" t="s">
         <v>382</v>
       </c>
     </row>
-    <row r="308" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
-      <c r="G308" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H308" s="1" t="s">
+    <row r="309" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+      <c r="G309" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H309" s="1" t="s">
         <v>383</v>
       </c>
     </row>
-    <row r="309" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
-      <c r="G309" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H309" s="1" t="s">
+    <row r="310" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+      <c r="G310" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H310" s="1" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="310" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
-      <c r="G310" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H310" s="1" t="s">
+    <row r="311" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+      <c r="G311" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H311" s="1" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="311" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
-      <c r="G311" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H311" s="1" t="s">
+    <row r="312" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+      <c r="G312" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H312" s="1" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="312" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
-      <c r="G312" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H312" s="1" t="s">
+    <row r="313" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+      <c r="G313" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H313" s="1" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="313" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
-      <c r="G313" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H313" s="1" t="s">
+    <row r="314" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+      <c r="G314" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H314" s="1" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="314" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
-      <c r="G314" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H314" s="1" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="315" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A315" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B315">
         <v>312</v>
@@ -9141,92 +9143,92 @@
         <v>20</v>
       </c>
       <c r="H315" s="1" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="316" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="316" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="G316" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H316" s="1" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="317" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+      <c r="G317" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H317" s="1" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="317" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
-      <c r="G317" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H317" s="1" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="318" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="G318" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H318" s="1" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="319" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+      <c r="G319" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H319" s="1" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="320" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+      <c r="G320" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H320" s="1" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="319" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
-      <c r="G319" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H319" s="1" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="320" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
-      <c r="G320" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H320" s="1" t="s">
+    <row r="321" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+      <c r="G321" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H321" s="1" t="s">
         <v>396</v>
       </c>
     </row>
-    <row r="321" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
-      <c r="G321" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H321" s="1" t="s">
+    <row r="322" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+      <c r="G322" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H322" s="1" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="322" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
-      <c r="G322" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H322" s="1" t="s">
+    <row r="323" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+      <c r="G323" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H323" s="1" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="323" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
-      <c r="G323" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H323" s="1" t="s">
+    <row r="324" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+      <c r="G324" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H324" s="1" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="324" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
-      <c r="G324" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H324" s="1" t="s">
+    <row r="325" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+      <c r="G325" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H325" s="1" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="325" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
-      <c r="G325" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H325" s="1" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="326" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A326" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B326">
         <v>75</v>
@@ -9248,12 +9250,12 @@
         <v>20</v>
       </c>
       <c r="H326" s="1" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="327" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="327" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A327" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B327">
         <v>198</v>
@@ -9275,12 +9277,12 @@
         <v>20</v>
       </c>
       <c r="H327" s="1" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="328" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="328" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A328" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B328">
         <v>534</v>
@@ -9302,12 +9304,12 @@
         <v>20</v>
       </c>
       <c r="H328" s="1" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="329" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="329" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A329" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B329">
         <v>133</v>
@@ -9329,12 +9331,12 @@
         <v>20</v>
       </c>
       <c r="H329" s="1" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="330" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="330" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A330" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B330">
         <v>229</v>
@@ -9356,12 +9358,12 @@
         <v>20</v>
       </c>
       <c r="H330" s="1" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="331" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="331" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A331" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B331">
         <v>421</v>
@@ -9383,12 +9385,12 @@
         <v>20</v>
       </c>
       <c r="H331" s="1" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="332" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="332" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A332" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B332">
         <v>429</v>
@@ -9410,12 +9412,12 @@
         <v>20</v>
       </c>
       <c r="H332" s="1" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="333" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="333" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A333" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B333">
         <v>437</v>
@@ -9437,12 +9439,12 @@
         <v>20</v>
       </c>
       <c r="H333" s="1" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="334" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="334" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A334" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B334">
         <v>450</v>
@@ -9464,12 +9466,12 @@
         <v>20</v>
       </c>
       <c r="H334" s="1" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="335" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="335" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A335" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B335">
         <v>14</v>
@@ -9491,28 +9493,28 @@
         <v>20</v>
       </c>
       <c r="H335" s="1" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="336" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="336" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="G336" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H336" s="1" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="337" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+      <c r="G337" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H337" s="1" t="s">
         <v>415</v>
       </c>
     </row>
-    <row r="337" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
-      <c r="G337" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H337" s="1" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="338" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="338" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A338" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B338">
         <v>16</v>
@@ -9534,28 +9536,28 @@
         <v>20</v>
       </c>
       <c r="H338" s="1" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="339" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="339" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="G339" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H339" s="1" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="340" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+      <c r="G340" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H340" s="1" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="340" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
-      <c r="G340" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H340" s="1" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="341" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A341" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B341">
         <v>1901</v>
@@ -9577,20 +9579,20 @@
         <v>20</v>
       </c>
       <c r="H341" s="1" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="342" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="342" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="G342" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H342" s="1" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="343" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="343" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A343" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B343">
         <v>108</v>
@@ -9612,12 +9614,12 @@
         <v>20</v>
       </c>
       <c r="H343" s="1" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="344" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="344" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A344" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B344">
         <v>208</v>
@@ -9639,12 +9641,12 @@
         <v>20</v>
       </c>
       <c r="H344" s="1" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="345" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="345" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A345" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B345">
         <v>255</v>
@@ -9666,12 +9668,12 @@
         <v>20</v>
       </c>
       <c r="H345" s="1" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="346" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="346" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A346" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B346">
         <v>300</v>
@@ -9693,12 +9695,12 @@
         <v>20</v>
       </c>
       <c r="H346" s="1" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="347" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="347" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A347" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B347">
         <v>422</v>
@@ -9720,12 +9722,12 @@
         <v>20</v>
       </c>
       <c r="H347" s="1" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="348" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="348" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A348" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B348">
         <v>522</v>
@@ -9747,12 +9749,12 @@
         <v>20</v>
       </c>
       <c r="H348" s="1" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="349" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="349" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A349" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B349">
         <v>555</v>
@@ -9774,12 +9776,12 @@
         <v>20</v>
       </c>
       <c r="H349" s="1" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="350" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="350" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A350" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B350">
         <v>604</v>
@@ -9801,12 +9803,12 @@
         <v>20</v>
       </c>
       <c r="H350" s="1" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="351" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="351" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A351" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B351">
         <v>692</v>
@@ -9828,12 +9830,12 @@
         <v>20</v>
       </c>
       <c r="H351" s="1" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="352" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="352" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A352" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B352">
         <v>59</v>
@@ -9855,20 +9857,20 @@
         <v>20</v>
       </c>
       <c r="H352" s="1" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="353" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="353" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="G353" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H353" s="1" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="354" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="354" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A354" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B354">
         <v>51</v>
@@ -9890,12 +9892,12 @@
         <v>20</v>
       </c>
       <c r="H354" s="1" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="355" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="355" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A355" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B355">
         <v>115</v>
@@ -9917,12 +9919,12 @@
         <v>20</v>
       </c>
       <c r="H355" s="1" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="356" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="356" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A356" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B356">
         <v>1338</v>
@@ -9944,12 +9946,12 @@
         <v>20</v>
       </c>
       <c r="H356" s="1" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="357" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="357" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A357" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B357">
         <v>29</v>
@@ -9971,12 +9973,12 @@
         <v>20</v>
       </c>
       <c r="H357" s="1" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="358" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="358" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A358" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B358">
         <v>1069</v>
@@ -9998,44 +10000,44 @@
         <v>20</v>
       </c>
       <c r="H358" s="1" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="359" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="359" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="G359" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H359" s="1" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="360" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+      <c r="G360" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H360" s="1" t="s">
         <v>444</v>
       </c>
     </row>
-    <row r="360" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
-      <c r="G360" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H360" s="1" t="s">
+    <row r="361" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+      <c r="G361" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H361" s="1" t="s">
         <v>445</v>
       </c>
     </row>
-    <row r="361" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
-      <c r="G361" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H361" s="1" t="s">
+    <row r="362" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+      <c r="G362" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H362" s="1" t="s">
         <v>446</v>
       </c>
     </row>
-    <row r="362" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
-      <c r="G362" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H362" s="1" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="363" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="363" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A363" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B363">
         <v>14</v>
@@ -10057,63 +10059,63 @@
         <v>20</v>
       </c>
       <c r="H363" s="1" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="364" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="364" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="G364" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H364" s="1" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="365" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+      <c r="G365" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H365" s="1" t="s">
         <v>450</v>
       </c>
     </row>
-    <row r="365" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
-      <c r="G365" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H365" s="1" t="s">
+    <row r="366" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+      <c r="G366" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H366" s="1" t="s">
         <v>451</v>
       </c>
     </row>
-    <row r="366" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
-      <c r="G366" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H366" s="1" t="s">
-        <v>452</v>
-      </c>
-    </row>
     <row r="367" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A367" t="s">
-        <v>454</v>
-      </c>
-      <c r="B367">
+      <c r="A367" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="B367" s="3">
         <v>16</v>
       </c>
-      <c r="C367">
+      <c r="C367" s="3">
         <v>163</v>
       </c>
-      <c r="D367">
+      <c r="D367" s="3">
         <v>64</v>
       </c>
-      <c r="E367">
+      <c r="E367" s="3">
         <v>4</v>
       </c>
-      <c r="F367" t="str" cm="1">
+      <c r="F367" s="3" t="str" cm="1">
         <f t="array" ref="F367">IF(AND(NOT(ISBLANK(C367:E367)),OR(C367&gt;=200,(D367+E367)&gt;40)),"Yes","No")</f>
         <v>Yes</v>
       </c>
-      <c r="G367" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H367" s="1" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="368" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+      <c r="G367" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H367" s="4" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="368" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A368" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B368">
         <v>54</v>
@@ -10135,28 +10137,28 @@
         <v>20</v>
       </c>
       <c r="H368" s="1" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="369" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="369" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="G369" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H369" s="1" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="370" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+      <c r="G370" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H370" s="1" t="s">
         <v>457</v>
       </c>
     </row>
-    <row r="370" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
-      <c r="G370" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H370" s="1" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="371" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="371" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A371" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B371">
         <v>44</v>
@@ -10178,12 +10180,12 @@
         <v>20</v>
       </c>
       <c r="H371" s="1" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="372" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="372" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A372" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B372">
         <v>43</v>
@@ -10205,12 +10207,12 @@
         <v>20</v>
       </c>
       <c r="H372" s="1" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="373" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="373" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A373" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B373">
         <v>11</v>
@@ -10232,12 +10234,12 @@
         <v>20</v>
       </c>
       <c r="H373" s="1" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="374" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="374" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A374" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B374">
         <v>41</v>
@@ -10259,12 +10261,12 @@
         <v>20</v>
       </c>
       <c r="H374" s="1" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="375" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="375" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A375" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B375">
         <v>104</v>
@@ -10286,12 +10288,12 @@
         <v>20</v>
       </c>
       <c r="H375" s="1" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="376" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="376" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A376" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B376">
         <v>127</v>
@@ -10313,12 +10315,12 @@
         <v>20</v>
       </c>
       <c r="H376" s="1" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="377" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="377" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A377" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B377">
         <v>27</v>
@@ -10340,12 +10342,12 @@
         <v>20</v>
       </c>
       <c r="H377" s="1" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="378" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A378" t="s">
         <v>468</v>
-      </c>
-    </row>
-    <row r="378" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A378" t="s">
-        <v>469</v>
       </c>
       <c r="B378">
         <v>48</v>
@@ -10367,12 +10369,12 @@
         <v>20</v>
       </c>
       <c r="H378" s="1" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="379" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="379" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A379" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B379">
         <v>65</v>
@@ -10394,12 +10396,12 @@
         <v>20</v>
       </c>
       <c r="H379" s="1" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="380" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="380" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A380" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B380">
         <v>86</v>
@@ -10421,12 +10423,12 @@
         <v>20</v>
       </c>
       <c r="H380" s="1" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="381" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="381" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A381" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B381">
         <v>97</v>
@@ -10448,12 +10450,12 @@
         <v>20</v>
       </c>
       <c r="H381" s="1" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="382" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="382" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A382" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B382">
         <v>170</v>
@@ -10475,12 +10477,12 @@
         <v>20</v>
       </c>
       <c r="H382" s="1" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="383" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="383" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A383" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B383">
         <v>255</v>
@@ -10502,36 +10504,36 @@
         <v>20</v>
       </c>
       <c r="H383" s="1" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="384" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="384" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="G384" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H384" s="1" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="385" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+      <c r="G385" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H385" s="1" t="s">
         <v>477</v>
       </c>
     </row>
-    <row r="385" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
-      <c r="G385" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H385" s="1" t="s">
+    <row r="386" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+      <c r="G386" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H386" s="1" t="s">
         <v>478</v>
       </c>
     </row>
-    <row r="386" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
-      <c r="G386" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H386" s="1" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="387" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="387" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A387" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B387">
         <v>85</v>
@@ -10553,12 +10555,12 @@
         <v>20</v>
       </c>
       <c r="H387" s="1" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="388" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="388" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A388" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B388">
         <v>149</v>
@@ -10580,12 +10582,12 @@
         <v>20</v>
       </c>
       <c r="H388" s="1" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="389" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="389" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A389" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B389">
         <v>157</v>
@@ -10607,12 +10609,12 @@
         <v>20</v>
       </c>
       <c r="H389" s="1" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="390" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="390" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A390" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B390">
         <v>792</v>
@@ -10634,12 +10636,12 @@
         <v>20</v>
       </c>
       <c r="H390" s="1" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="391" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="391" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A391" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B391">
         <v>817</v>
@@ -10661,12 +10663,12 @@
         <v>20</v>
       </c>
       <c r="H391" s="1" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="392" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="392" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A392" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B392">
         <v>835</v>
@@ -10688,12 +10690,12 @@
         <v>20</v>
       </c>
       <c r="H392" s="1" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="393" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="393" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A393" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B393">
         <v>856</v>
@@ -10715,12 +10717,12 @@
         <v>20</v>
       </c>
       <c r="H393" s="1" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="394" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="394" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A394" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B394">
         <v>872</v>
@@ -10742,12 +10744,12 @@
         <v>20</v>
       </c>
       <c r="H394" s="1" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="395" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="395" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A395" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B395">
         <v>888</v>
@@ -10769,12 +10771,12 @@
         <v>20</v>
       </c>
       <c r="H395" s="1" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="396" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="396" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A396" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B396">
         <v>898</v>
@@ -10796,12 +10798,12 @@
         <v>20</v>
       </c>
       <c r="H396" s="1" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="397" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="397" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A397" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B397">
         <v>972</v>
@@ -10823,12 +10825,12 @@
         <v>20</v>
       </c>
       <c r="H397" s="1" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="398" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="398" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A398" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B398">
         <v>1120</v>
@@ -10850,12 +10852,12 @@
         <v>20</v>
       </c>
       <c r="H398" s="1" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="399" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="399" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A399" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="B399">
         <v>2377</v>
@@ -10877,12 +10879,12 @@
         <v>20</v>
       </c>
       <c r="H399" s="1" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="400" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="400" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A400" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B400">
         <v>2594</v>
@@ -10904,39 +10906,39 @@
         <v>20</v>
       </c>
       <c r="H400" s="1" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="401" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.2">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="401" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A401" s="2" t="s">
-        <v>495</v>
-      </c>
-      <c r="B401" s="2">
+        <v>494</v>
+      </c>
+      <c r="B401" s="3">
         <v>2702</v>
       </c>
-      <c r="C401" s="2">
+      <c r="C401" s="3">
         <v>1272</v>
       </c>
-      <c r="D401" s="2">
+      <c r="D401" s="3">
         <v>102</v>
       </c>
-      <c r="E401" s="2">
+      <c r="E401" s="3">
         <v>18</v>
       </c>
-      <c r="F401" s="2" t="str" cm="1">
+      <c r="F401" s="3" t="str" cm="1">
         <f t="array" ref="F401">IF(AND(NOT(ISBLANK(C401:E401)),OR(C401&gt;=200,(D401+E401)&gt;40)),"Yes","No")</f>
         <v>Yes</v>
       </c>
-      <c r="G401" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="H401" s="3" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="402" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+      <c r="G401" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H401" s="4" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="402" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A402" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B402">
         <v>6228</v>
@@ -10958,12 +10960,12 @@
         <v>20</v>
       </c>
       <c r="H402" s="1" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="403" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="403" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A403" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B403">
         <v>6423</v>
@@ -10985,12 +10987,12 @@
         <v>20</v>
       </c>
       <c r="H403" s="1" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="404" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="404" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A404" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B404">
         <v>6618</v>
@@ -11012,12 +11014,12 @@
         <v>20</v>
       </c>
       <c r="H404" s="1" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="405" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="405" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A405" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B405">
         <v>6713</v>
@@ -11039,12 +11041,12 @@
         <v>20</v>
       </c>
       <c r="H405" s="1" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="406" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="406" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A406" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B406">
         <v>8075</v>
@@ -11066,12 +11068,12 @@
         <v>20</v>
       </c>
       <c r="H406" s="1" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="407" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="407" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A407" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B407">
         <v>215</v>
@@ -11093,12 +11095,12 @@
         <v>20</v>
       </c>
       <c r="H407" s="1" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="408" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="408" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A408" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B408">
         <v>265</v>
@@ -11120,12 +11122,12 @@
         <v>20</v>
       </c>
       <c r="H408" s="1" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="409" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="409" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A409" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B409">
         <v>283</v>
@@ -11147,12 +11149,12 @@
         <v>20</v>
       </c>
       <c r="H409" s="1" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="410" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="410" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A410" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B410">
         <v>296</v>
@@ -11174,12 +11176,12 @@
         <v>20</v>
       </c>
       <c r="H410" s="1" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="411" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="411" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A411" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="B411">
         <v>321</v>
@@ -11201,12 +11203,12 @@
         <v>20</v>
       </c>
       <c r="H411" s="1" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="412" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="412" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A412" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B412">
         <v>1467</v>
@@ -11228,12 +11230,12 @@
         <v>20</v>
       </c>
       <c r="H412" s="1" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="413" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="413" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A413" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B413">
         <v>1497</v>
@@ -11255,90 +11257,90 @@
         <v>20</v>
       </c>
       <c r="H413" s="1" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="414" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.2">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="414" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A414" s="2" t="s">
-        <v>510</v>
-      </c>
-      <c r="B414" s="2">
+        <v>509</v>
+      </c>
+      <c r="B414" s="3">
         <v>86</v>
       </c>
-      <c r="C414" s="2">
+      <c r="C414" s="3">
         <v>245</v>
       </c>
-      <c r="D414" s="2">
+      <c r="D414" s="3">
         <v>18</v>
       </c>
-      <c r="E414" s="2">
+      <c r="E414" s="3">
         <v>13</v>
       </c>
-      <c r="F414" s="2" t="str" cm="1">
+      <c r="F414" s="3" t="str" cm="1">
         <f t="array" ref="F414">IF(AND(NOT(ISBLANK(C414:E414)),OR(C414&gt;=200,(D414+E414)&gt;40)),"Yes","No")</f>
         <v>Yes</v>
       </c>
-      <c r="G414" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="H414" s="3" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="415" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+      <c r="G414" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H414" s="4" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="415" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="G415" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H415" s="1" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="416" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A416" t="s">
-        <v>513</v>
-      </c>
-      <c r="B416">
+      <c r="A416" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="B416" s="3">
         <v>16</v>
       </c>
-      <c r="C416">
+      <c r="C416" s="3">
         <v>325</v>
       </c>
-      <c r="D416">
+      <c r="D416" s="3">
         <v>13</v>
       </c>
-      <c r="E416">
+      <c r="E416" s="3">
         <v>30</v>
       </c>
-      <c r="F416" t="str" cm="1">
+      <c r="F416" s="3" t="str" cm="1">
         <f t="array" ref="F416">IF(AND(NOT(ISBLANK(C416:E416)),OR(C416&gt;=200,(D416+E416)&gt;40)),"Yes","No")</f>
         <v>Yes</v>
       </c>
-      <c r="G416" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H416" s="1" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="417" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+      <c r="G416" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H416" s="4" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="417" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="G417" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H417" s="1" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="418" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+      <c r="G418" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H418" s="1" t="s">
         <v>514</v>
       </c>
     </row>
-    <row r="418" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
-      <c r="G418" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H418" s="1" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="419" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="419" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A419" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B419">
         <v>73</v>
@@ -11360,63 +11362,63 @@
         <v>20</v>
       </c>
       <c r="H419" s="1" t="s">
-        <v>516</v>
-      </c>
-    </row>
-    <row r="420" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="420" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="G420" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H420" s="1" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="421" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+      <c r="G421" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H421" s="1" t="s">
         <v>518</v>
       </c>
     </row>
-    <row r="421" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
-      <c r="G421" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H421" s="1" t="s">
+    <row r="422" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+      <c r="G422" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H422" s="1" t="s">
         <v>519</v>
       </c>
     </row>
-    <row r="422" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
-      <c r="G422" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H422" s="1" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="423" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A423" s="2" t="s">
-        <v>522</v>
-      </c>
-      <c r="B423" s="2">
+    <row r="423" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A423" s="3" t="s">
+        <v>521</v>
+      </c>
+      <c r="B423" s="3">
         <v>18</v>
       </c>
-      <c r="C423" s="2">
+      <c r="C423" s="3">
         <v>469</v>
       </c>
-      <c r="D423" s="2">
+      <c r="D423" s="3">
         <v>50</v>
       </c>
-      <c r="E423" s="2">
-        <v>9</v>
-      </c>
-      <c r="F423" s="2" t="str" cm="1">
+      <c r="E423" s="3">
+        <v>9</v>
+      </c>
+      <c r="F423" s="3" t="str" cm="1">
         <f t="array" ref="F423">IF(AND(NOT(ISBLANK(C423:E423)),OR(C423&gt;=200,(D423+E423)&gt;40)),"Yes","No")</f>
         <v>Yes</v>
       </c>
-      <c r="G423" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="H423" s="3" t="s">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="424" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+      <c r="G423" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H423" s="4" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="424" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A424" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B424">
         <v>1982</v>
@@ -11438,12 +11440,12 @@
         <v>20</v>
       </c>
       <c r="H424" s="1" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="425" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="425" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A425" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="B425">
         <v>1635</v>
@@ -11465,12 +11467,12 @@
         <v>20</v>
       </c>
       <c r="H425" s="1" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="426" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="426" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A426" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B426">
         <v>1641</v>
@@ -11492,12 +11494,12 @@
         <v>20</v>
       </c>
       <c r="H426" s="1" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="427" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="427" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A427" s="1" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B427">
         <v>1591</v>
@@ -11519,12 +11521,12 @@
         <v>20</v>
       </c>
       <c r="H427" s="1" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="428" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="428" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A428" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B428">
         <v>1608</v>
@@ -11546,12 +11548,12 @@
         <v>20</v>
       </c>
       <c r="H428" s="1" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="429" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="429" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A429" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B429">
         <v>1456</v>
@@ -11573,12 +11575,12 @@
         <v>20</v>
       </c>
       <c r="H429" s="1" t="s">
-        <v>533</v>
-      </c>
-    </row>
-    <row r="430" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="430" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A430" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B430">
         <v>60</v>
@@ -11600,12 +11602,12 @@
         <v>20</v>
       </c>
       <c r="H430" s="1" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="431" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A431" t="s">
         <v>535</v>
-      </c>
-    </row>
-    <row r="431" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A431" t="s">
-        <v>536</v>
       </c>
       <c r="B431">
         <v>64</v>
@@ -11627,12 +11629,12 @@
         <v>20</v>
       </c>
       <c r="H431" s="1" t="s">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="432" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="432" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A432" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="B432">
         <v>68</v>
@@ -11654,12 +11656,12 @@
         <v>20</v>
       </c>
       <c r="H432" s="1" t="s">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="433" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="433" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A433" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="B433">
         <v>81</v>
@@ -11681,622 +11683,622 @@
         <v>20</v>
       </c>
       <c r="H433" s="1" t="s">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="434" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="434" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="G434" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H434" s="1" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="435" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+      <c r="G435" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H435" s="1" t="s">
         <v>539</v>
       </c>
     </row>
-    <row r="435" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
-      <c r="G435" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H435" s="1" t="s">
+    <row r="436" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+      <c r="G436" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H436" s="1" t="s">
         <v>540</v>
       </c>
     </row>
-    <row r="436" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
-      <c r="G436" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H436" s="1" t="s">
+    <row r="437" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+      <c r="G437" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H437" s="1" t="s">
         <v>541</v>
       </c>
     </row>
-    <row r="437" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
-      <c r="G437" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H437" s="1" t="s">
+    <row r="438" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+      <c r="G438" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H438" s="1" t="s">
         <v>542</v>
       </c>
     </row>
-    <row r="438" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
-      <c r="G438" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H438" s="1" t="s">
+    <row r="439" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+      <c r="G439" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H439" s="1" t="s">
         <v>543</v>
       </c>
     </row>
-    <row r="439" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
-      <c r="G439" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H439" s="1" t="s">
+    <row r="440" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+      <c r="G440" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H440" s="1" t="s">
         <v>544</v>
       </c>
     </row>
-    <row r="440" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
-      <c r="G440" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H440" s="1" t="s">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="441" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="441" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="G441" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H441" s="1" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="442" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+      <c r="G442" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H442" s="1" t="s">
         <v>547</v>
       </c>
     </row>
-    <row r="442" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
-      <c r="G442" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H442" s="1" t="s">
+    <row r="443" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+      <c r="G443" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H443" s="1" t="s">
         <v>548</v>
       </c>
     </row>
-    <row r="443" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
-      <c r="G443" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H443" s="1" t="s">
+    <row r="444" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+      <c r="G444" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H444" s="1" t="s">
         <v>549</v>
       </c>
     </row>
-    <row r="444" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
-      <c r="G444" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H444" s="1" t="s">
+    <row r="445" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+      <c r="G445" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H445" s="1" t="s">
         <v>550</v>
       </c>
     </row>
-    <row r="445" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
-      <c r="G445" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H445" s="1" t="s">
+    <row r="446" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+      <c r="G446" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H446" s="1" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="446" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
-      <c r="G446" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H446" s="1" t="s">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="447" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="447" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="G447" s="1"/>
       <c r="H447" s="1"/>
     </row>
-    <row r="448" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="448" spans="1:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="G448" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H448" s="1" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="449" spans="7:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+      <c r="G449" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H449" s="1" t="s">
         <v>554</v>
       </c>
     </row>
-    <row r="449" spans="7:8" hidden="1" x14ac:dyDescent="0.2">
-      <c r="G449" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H449" s="1" t="s">
+    <row r="450" spans="7:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+      <c r="G450" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H450" s="1" t="s">
         <v>555</v>
       </c>
     </row>
-    <row r="450" spans="7:8" hidden="1" x14ac:dyDescent="0.2">
-      <c r="G450" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H450" s="1" t="s">
+    <row r="451" spans="7:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+      <c r="G451" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H451" s="1" t="s">
         <v>556</v>
       </c>
     </row>
-    <row r="451" spans="7:8" hidden="1" x14ac:dyDescent="0.2">
-      <c r="G451" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H451" s="1" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="452" spans="7:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="452" spans="7:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="G452" s="1"/>
       <c r="H452" s="1"/>
     </row>
-    <row r="453" spans="7:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="453" spans="7:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="G453" s="1"/>
       <c r="H453" s="1"/>
     </row>
-    <row r="454" spans="7:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="454" spans="7:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="G454" s="1"/>
       <c r="H454" s="1"/>
     </row>
-    <row r="455" spans="7:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="455" spans="7:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="G455" s="1"/>
       <c r="H455" s="1"/>
     </row>
-    <row r="456" spans="7:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="456" spans="7:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="G456" s="1"/>
       <c r="H456" s="1"/>
     </row>
-    <row r="457" spans="7:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="457" spans="7:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="G457" s="1"/>
       <c r="H457" s="1"/>
     </row>
-    <row r="458" spans="7:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="458" spans="7:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="G458" s="1"/>
       <c r="H458" s="1"/>
     </row>
-    <row r="459" spans="7:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="459" spans="7:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="G459" s="1"/>
       <c r="H459" s="1"/>
     </row>
-    <row r="460" spans="7:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="460" spans="7:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="G460" s="1"/>
       <c r="H460" s="1"/>
     </row>
-    <row r="461" spans="7:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="461" spans="7:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="G461" s="1"/>
       <c r="H461" s="1"/>
     </row>
-    <row r="462" spans="7:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="462" spans="7:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="G462" s="1"/>
       <c r="H462" s="1"/>
     </row>
-    <row r="463" spans="7:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="463" spans="7:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="G463" s="1"/>
       <c r="H463" s="1"/>
     </row>
-    <row r="464" spans="7:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="464" spans="7:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="G464" s="1"/>
       <c r="H464" s="1"/>
     </row>
-    <row r="465" spans="6:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="465" spans="6:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="G465" s="1"/>
       <c r="H465" s="1"/>
     </row>
-    <row r="466" spans="6:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="466" spans="6:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="G466" s="1"/>
       <c r="H466" s="1"/>
     </row>
-    <row r="467" spans="6:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="467" spans="6:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="G467" s="1"/>
       <c r="H467" s="1"/>
     </row>
-    <row r="468" spans="6:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="468" spans="6:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="G468" s="1"/>
       <c r="H468" s="1"/>
     </row>
-    <row r="469" spans="6:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="469" spans="6:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="G469" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H469" s="1" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="470" spans="6:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+      <c r="G470" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H470" s="1" t="s">
         <v>562</v>
       </c>
     </row>
-    <row r="470" spans="6:8" hidden="1" x14ac:dyDescent="0.2">
-      <c r="G470" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H470" s="1" t="s">
+    <row r="471" spans="6:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+      <c r="G471" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H471" s="1" t="s">
         <v>563</v>
       </c>
     </row>
-    <row r="471" spans="6:8" hidden="1" x14ac:dyDescent="0.2">
-      <c r="G471" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H471" s="1" t="s">
-        <v>564</v>
-      </c>
-    </row>
-    <row r="472" spans="6:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="472" spans="6:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="G472" s="1"/>
       <c r="H472" s="1"/>
     </row>
-    <row r="473" spans="6:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="473" spans="6:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="G473" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H473" s="1" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="474" spans="6:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+      <c r="G474" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H474" s="1" t="s">
         <v>566</v>
       </c>
     </row>
-    <row r="474" spans="6:8" hidden="1" x14ac:dyDescent="0.2">
-      <c r="G474" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H474" s="1" t="s">
+    <row r="475" spans="6:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+      <c r="G475" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H475" s="1" t="s">
         <v>567</v>
       </c>
     </row>
-    <row r="475" spans="6:8" hidden="1" x14ac:dyDescent="0.2">
-      <c r="G475" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H475" s="1" t="s">
-        <v>568</v>
-      </c>
-    </row>
-    <row r="476" spans="6:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="476" spans="6:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="G476" s="1"/>
       <c r="H476" s="1"/>
     </row>
-    <row r="477" spans="6:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="477" spans="6:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="G477" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H477" s="1" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="478" spans="6:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+      <c r="G478" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H478" s="1" t="s">
         <v>570</v>
       </c>
     </row>
-    <row r="478" spans="6:8" hidden="1" x14ac:dyDescent="0.2">
-      <c r="G478" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H478" s="1" t="s">
+    <row r="479" spans="6:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+      <c r="G479" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H479" s="1" t="s">
         <v>571</v>
       </c>
     </row>
-    <row r="479" spans="6:8" hidden="1" x14ac:dyDescent="0.2">
-      <c r="G479" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H479" s="1" t="s">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="480" spans="6:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="480" spans="6:8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="F480" t="str" cm="1">
         <f t="array" ref="F480">IF(AND(NOT(ISBLANK(C480:E480)),OR(C480&gt;=200,(D480+E480)&gt;40)),"Yes","No")</f>
         <v>No</v>
       </c>
     </row>
-    <row r="481" spans="6:6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="481" spans="6:6" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="F481" t="str" cm="1">
         <f t="array" ref="F481">IF(AND(NOT(ISBLANK(C481:E481)),OR(C481&gt;=200,(D481+E481)&gt;40)),"Yes","No")</f>
         <v>No</v>
       </c>
     </row>
-    <row r="482" spans="6:6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="482" spans="6:6" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="F482" t="str" cm="1">
         <f t="array" ref="F482">IF(AND(NOT(ISBLANK(C482:E482)),OR(C482&gt;=200,(D482+E482)&gt;40)),"Yes","No")</f>
         <v>No</v>
       </c>
     </row>
-    <row r="483" spans="6:6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="483" spans="6:6" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="F483" t="str" cm="1">
         <f t="array" ref="F483">IF(AND(NOT(ISBLANK(C483:E483)),OR(C483&gt;=200,(D483+E483)&gt;40)),"Yes","No")</f>
         <v>No</v>
       </c>
     </row>
-    <row r="484" spans="6:6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="484" spans="6:6" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="F484" t="str" cm="1">
         <f t="array" ref="F484">IF(AND(NOT(ISBLANK(C484:E484)),OR(C484&gt;=200,(D484+E484)&gt;40)),"Yes","No")</f>
         <v>No</v>
       </c>
     </row>
-    <row r="485" spans="6:6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="485" spans="6:6" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="F485" t="str" cm="1">
         <f t="array" ref="F485">IF(AND(NOT(ISBLANK(C485:E485)),OR(C485&gt;=200,(D485+E485)&gt;40)),"Yes","No")</f>
         <v>No</v>
       </c>
     </row>
-    <row r="486" spans="6:6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="486" spans="6:6" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="F486" t="str" cm="1">
         <f t="array" ref="F486">IF(AND(NOT(ISBLANK(C486:E486)),OR(C486&gt;=200,(D486+E486)&gt;40)),"Yes","No")</f>
         <v>No</v>
       </c>
     </row>
-    <row r="487" spans="6:6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="487" spans="6:6" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="F487" t="str" cm="1">
         <f t="array" ref="F487">IF(AND(NOT(ISBLANK(C487:E487)),OR(C487&gt;=200,(D487+E487)&gt;40)),"Yes","No")</f>
         <v>No</v>
       </c>
     </row>
-    <row r="488" spans="6:6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="488" spans="6:6" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="F488" t="str" cm="1">
         <f t="array" ref="F488">IF(AND(NOT(ISBLANK(C488:E488)),OR(C488&gt;=200,(D488+E488)&gt;40)),"Yes","No")</f>
         <v>No</v>
       </c>
     </row>
-    <row r="489" spans="6:6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="489" spans="6:6" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="F489" t="str" cm="1">
         <f t="array" ref="F489">IF(AND(NOT(ISBLANK(C489:E489)),OR(C489&gt;=200,(D489+E489)&gt;40)),"Yes","No")</f>
         <v>No</v>
       </c>
     </row>
-    <row r="490" spans="6:6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="490" spans="6:6" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="F490" t="str" cm="1">
         <f t="array" ref="F490">IF(AND(NOT(ISBLANK(C490:E490)),OR(C490&gt;=200,(D490+E490)&gt;40)),"Yes","No")</f>
         <v>No</v>
       </c>
     </row>
-    <row r="491" spans="6:6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="491" spans="6:6" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="F491" t="str" cm="1">
         <f t="array" ref="F491">IF(AND(NOT(ISBLANK(C491:E491)),OR(C491&gt;=200,(D491+E491)&gt;40)),"Yes","No")</f>
         <v>No</v>
       </c>
     </row>
-    <row r="492" spans="6:6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="492" spans="6:6" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="F492" t="str" cm="1">
         <f t="array" ref="F492">IF(AND(NOT(ISBLANK(C492:E492)),OR(C492&gt;=200,(D492+E492)&gt;40)),"Yes","No")</f>
         <v>No</v>
       </c>
     </row>
-    <row r="493" spans="6:6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="493" spans="6:6" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="F493" t="str" cm="1">
         <f t="array" ref="F493">IF(AND(NOT(ISBLANK(C493:E493)),OR(C493&gt;=200,(D493+E493)&gt;40)),"Yes","No")</f>
         <v>No</v>
       </c>
     </row>
-    <row r="494" spans="6:6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="494" spans="6:6" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="F494" t="str" cm="1">
         <f t="array" ref="F494">IF(AND(NOT(ISBLANK(C494:E494)),OR(C494&gt;=200,(D494+E494)&gt;40)),"Yes","No")</f>
         <v>No</v>
       </c>
     </row>
-    <row r="495" spans="6:6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="495" spans="6:6" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="F495" t="str" cm="1">
         <f t="array" ref="F495">IF(AND(NOT(ISBLANK(C495:E495)),OR(C495&gt;=200,(D495+E495)&gt;40)),"Yes","No")</f>
         <v>No</v>
       </c>
     </row>
-    <row r="496" spans="6:6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="496" spans="6:6" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="F496" t="str" cm="1">
         <f t="array" ref="F496">IF(AND(NOT(ISBLANK(C496:E496)),OR(C496&gt;=200,(D496+E496)&gt;40)),"Yes","No")</f>
         <v>No</v>
       </c>
     </row>
-    <row r="497" spans="6:6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="497" spans="6:6" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="F497" t="str" cm="1">
         <f t="array" ref="F497">IF(AND(NOT(ISBLANK(C497:E497)),OR(C497&gt;=200,(D497+E497)&gt;40)),"Yes","No")</f>
         <v>No</v>
       </c>
     </row>
-    <row r="498" spans="6:6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="498" spans="6:6" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="F498" t="str" cm="1">
         <f t="array" ref="F498">IF(AND(NOT(ISBLANK(C498:E498)),OR(C498&gt;=200,(D498+E498)&gt;40)),"Yes","No")</f>
         <v>No</v>
       </c>
     </row>
-    <row r="499" spans="6:6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="499" spans="6:6" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="F499" t="str" cm="1">
         <f t="array" ref="F499">IF(AND(NOT(ISBLANK(C499:E499)),OR(C499&gt;=200,(D499+E499)&gt;40)),"Yes","No")</f>
         <v>No</v>
       </c>
     </row>
-    <row r="500" spans="6:6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="500" spans="6:6" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="F500" t="str" cm="1">
         <f t="array" ref="F500">IF(AND(NOT(ISBLANK(C500:E500)),OR(C500&gt;=200,(D500+E500)&gt;40)),"Yes","No")</f>
         <v>No</v>
       </c>
     </row>
-    <row r="501" spans="6:6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="501" spans="6:6" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="F501" t="str" cm="1">
         <f t="array" ref="F501">IF(AND(NOT(ISBLANK(C501:E501)),OR(C501&gt;=200,(D501+E501)&gt;40)),"Yes","No")</f>
         <v>No</v>
       </c>
     </row>
-    <row r="502" spans="6:6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="502" spans="6:6" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="F502" t="str" cm="1">
         <f t="array" ref="F502">IF(AND(NOT(ISBLANK(C502:E502)),OR(C502&gt;=200,(D502+E502)&gt;40)),"Yes","No")</f>
         <v>No</v>
       </c>
     </row>
-    <row r="503" spans="6:6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="503" spans="6:6" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="F503" t="str" cm="1">
         <f t="array" ref="F503">IF(AND(NOT(ISBLANK(C503:E503)),OR(C503&gt;=200,(D503+E503)&gt;40)),"Yes","No")</f>
         <v>No</v>
       </c>
     </row>
-    <row r="504" spans="6:6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="504" spans="6:6" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="F504" t="str" cm="1">
         <f t="array" ref="F504">IF(AND(NOT(ISBLANK(C504:E504)),OR(C504&gt;=200,(D504+E504)&gt;40)),"Yes","No")</f>
         <v>No</v>
       </c>
     </row>
-    <row r="505" spans="6:6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="505" spans="6:6" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="F505" t="str" cm="1">
         <f t="array" ref="F505">IF(AND(NOT(ISBLANK(C505:E505)),OR(C505&gt;=200,(D505+E505)&gt;40)),"Yes","No")</f>
         <v>No</v>
       </c>
     </row>
-    <row r="506" spans="6:6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="506" spans="6:6" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="F506" t="str" cm="1">
         <f t="array" ref="F506">IF(AND(NOT(ISBLANK(C506:E506)),OR(C506&gt;=200,(D506+E506)&gt;40)),"Yes","No")</f>
         <v>No</v>
       </c>
     </row>
-    <row r="507" spans="6:6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="507" spans="6:6" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="F507" t="str" cm="1">
         <f t="array" ref="F507">IF(AND(NOT(ISBLANK(C507:E507)),OR(C507&gt;=200,(D507+E507)&gt;40)),"Yes","No")</f>
         <v>No</v>
       </c>
     </row>
-    <row r="508" spans="6:6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="508" spans="6:6" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="F508" t="str" cm="1">
         <f t="array" ref="F508">IF(AND(NOT(ISBLANK(C508:E508)),OR(C508&gt;=200,(D508+E508)&gt;40)),"Yes","No")</f>
         <v>No</v>
       </c>
     </row>
-    <row r="509" spans="6:6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="509" spans="6:6" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="F509" t="str" cm="1">
         <f t="array" ref="F509">IF(AND(NOT(ISBLANK(C509:E509)),OR(C509&gt;=200,(D509+E509)&gt;40)),"Yes","No")</f>
         <v>No</v>
       </c>
     </row>
-    <row r="510" spans="6:6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="510" spans="6:6" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="F510" t="str" cm="1">
         <f t="array" ref="F510">IF(AND(NOT(ISBLANK(C510:E510)),OR(C510&gt;=200,(D510+E510)&gt;40)),"Yes","No")</f>
         <v>No</v>
       </c>
     </row>
-    <row r="511" spans="6:6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="511" spans="6:6" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="F511" t="str" cm="1">
         <f t="array" ref="F511">IF(AND(NOT(ISBLANK(C511:E511)),OR(C511&gt;=200,(D511+E511)&gt;40)),"Yes","No")</f>
         <v>No</v>
       </c>
     </row>
-    <row r="512" spans="6:6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="512" spans="6:6" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="F512" t="str" cm="1">
         <f t="array" ref="F512">IF(AND(NOT(ISBLANK(C512:E512)),OR(C512&gt;=200,(D512+E512)&gt;40)),"Yes","No")</f>
         <v>No</v>
       </c>
     </row>
-    <row r="513" spans="6:6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="513" spans="6:6" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="F513" t="str" cm="1">
         <f t="array" ref="F513">IF(AND(NOT(ISBLANK(C513:E513)),OR(C513&gt;=200,(D513+E513)&gt;40)),"Yes","No")</f>
         <v>No</v>
       </c>
     </row>
-    <row r="514" spans="6:6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="514" spans="6:6" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="F514" t="str" cm="1">
         <f t="array" ref="F514">IF(AND(NOT(ISBLANK(C514:E514)),OR(C514&gt;=200,(D514+E514)&gt;40)),"Yes","No")</f>
         <v>No</v>
       </c>
     </row>
-    <row r="515" spans="6:6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="515" spans="6:6" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="F515" t="str" cm="1">
         <f t="array" ref="F515">IF(AND(NOT(ISBLANK(C515:E515)),OR(C515&gt;=200,(D515+E515)&gt;40)),"Yes","No")</f>
         <v>No</v>
       </c>
     </row>
-    <row r="516" spans="6:6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="516" spans="6:6" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="F516" t="str" cm="1">
         <f t="array" ref="F516">IF(AND(NOT(ISBLANK(C516:E516)),OR(C516&gt;=200,(D516+E516)&gt;40)),"Yes","No")</f>
         <v>No</v>
       </c>
     </row>
-    <row r="517" spans="6:6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="517" spans="6:6" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="F517" t="str" cm="1">
         <f t="array" ref="F517">IF(AND(NOT(ISBLANK(C517:E517)),OR(C517&gt;=200,(D517+E517)&gt;40)),"Yes","No")</f>
         <v>No</v>
       </c>
     </row>
-    <row r="518" spans="6:6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="518" spans="6:6" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="F518" t="str" cm="1">
         <f t="array" ref="F518">IF(AND(NOT(ISBLANK(C518:E518)),OR(C518&gt;=200,(D518+E518)&gt;40)),"Yes","No")</f>
         <v>No</v>
       </c>
     </row>
-    <row r="519" spans="6:6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="519" spans="6:6" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="F519" t="str" cm="1">
         <f t="array" ref="F519">IF(AND(NOT(ISBLANK(C519:E519)),OR(C519&gt;=200,(D519+E519)&gt;40)),"Yes","No")</f>
         <v>No</v>
       </c>
     </row>
-    <row r="520" spans="6:6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="520" spans="6:6" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="F520" t="str" cm="1">
         <f t="array" ref="F520">IF(AND(NOT(ISBLANK(C520:E520)),OR(C520&gt;=200,(D520+E520)&gt;40)),"Yes","No")</f>
         <v>No</v>
       </c>
     </row>
-    <row r="521" spans="6:6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="521" spans="6:6" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="F521" t="str" cm="1">
         <f t="array" ref="F521">IF(AND(NOT(ISBLANK(C521:E521)),OR(C521&gt;=200,(D521+E521)&gt;40)),"Yes","No")</f>
         <v>No</v>
       </c>
     </row>
-    <row r="522" spans="6:6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="522" spans="6:6" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="F522" t="str" cm="1">
         <f t="array" ref="F522">IF(AND(NOT(ISBLANK(C522:E522)),OR(C522&gt;=200,(D522+E522)&gt;40)),"Yes","No")</f>
         <v>No</v>
       </c>
     </row>
-    <row r="523" spans="6:6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="523" spans="6:6" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="F523" t="str" cm="1">
         <f t="array" ref="F523">IF(AND(NOT(ISBLANK(C523:E523)),OR(C523&gt;=200,(D523+E523)&gt;40)),"Yes","No")</f>
         <v>No</v>
       </c>
     </row>
-    <row r="524" spans="6:6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="524" spans="6:6" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="F524" t="str" cm="1">
         <f t="array" ref="F524">IF(AND(NOT(ISBLANK(C524:E524)),OR(C524&gt;=200,(D524+E524)&gt;40)),"Yes","No")</f>
         <v>No</v>
       </c>
     </row>
-    <row r="525" spans="6:6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="525" spans="6:6" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="F525" t="str" cm="1">
         <f t="array" ref="F525">IF(AND(NOT(ISBLANK(C525:E525)),OR(C525&gt;=200,(D525+E525)&gt;40)),"Yes","No")</f>
         <v>No</v>
       </c>
     </row>
-    <row r="526" spans="6:6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="526" spans="6:6" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="F526" t="str" cm="1">
         <f t="array" ref="F526">IF(AND(NOT(ISBLANK(C526:E526)),OR(C526&gt;=200,(D526+E526)&gt;40)),"Yes","No")</f>
         <v>No</v>
       </c>
     </row>
-    <row r="527" spans="6:6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="527" spans="6:6" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="F527" t="str" cm="1">
         <f t="array" ref="F527">IF(AND(NOT(ISBLANK(C527:E527)),OR(C527&gt;=200,(D527+E527)&gt;40)),"Yes","No")</f>
         <v>No</v>
       </c>
     </row>
-    <row r="528" spans="6:6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="528" spans="6:6" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="F528" t="str" cm="1">
         <f t="array" ref="F528">IF(AND(NOT(ISBLANK(C528:E528)),OR(C528&gt;=200,(D528+E528)&gt;40)),"Yes","No")</f>
         <v>No</v>
       </c>
     </row>
-    <row r="529" spans="6:6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="529" spans="6:6" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="F529" t="str" cm="1">
         <f t="array" ref="F529">IF(AND(NOT(ISBLANK(C529:E529)),OR(C529&gt;=200,(D529+E529)&gt;40)),"Yes","No")</f>
         <v>No</v>
       </c>
     </row>
-    <row r="530" spans="6:6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="530" spans="6:6" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="F530" t="str" cm="1">
         <f t="array" ref="F530">IF(AND(NOT(ISBLANK(C530:E530)),OR(C530&gt;=200,(D530+E530)&gt;40)),"Yes","No")</f>
         <v>No</v>
       </c>
     </row>
-    <row r="531" spans="6:6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="531" spans="6:6" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="F531" t="str" cm="1">
         <f t="array" ref="F531">IF(AND(NOT(ISBLANK(C531:E531)),OR(C531&gt;=200,(D531+E531)&gt;40)),"Yes","No")</f>
         <v>No</v>
       </c>
     </row>
-    <row r="532" spans="6:6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="532" spans="6:6" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="F532" t="str" cm="1">
         <f t="array" ref="F532">IF(AND(NOT(ISBLANK(C532:E532)),OR(C532&gt;=200,(D532+E532)&gt;40)),"Yes","No")</f>
         <v>No</v>
       </c>
     </row>
-    <row r="533" spans="6:6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="533" spans="6:6" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="F533" t="str" cm="1">
         <f t="array" ref="F533">IF(AND(NOT(ISBLANK(C533:E533)),OR(C533&gt;=200,(D533+E533)&gt;40)),"Yes","No")</f>
         <v>No</v>
       </c>
     </row>
-    <row r="534" spans="6:6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="534" spans="6:6" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="F534" t="str" cm="1">
         <f t="array" ref="F534">IF(AND(NOT(ISBLANK(C534:E534)),OR(C534&gt;=200,(D534+E534)&gt;40)),"Yes","No")</f>
         <v>No</v>
@@ -12606,937 +12608,937 @@
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A59" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A61" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A62" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A63" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A64" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A65" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A66" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A67" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A68" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A69" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A70" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A71" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A72" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A73" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A74" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A75" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A76" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A77" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A78" s="1" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A79" s="1" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A80" s="1" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A81" s="1" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A82" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A83" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A84" s="1" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A85" s="1" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A86" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="87" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A87" s="1" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="88" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A88" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="89" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A89" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A90" s="1" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A91" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="92" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A92" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="93" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A93" s="1" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="94" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A94" s="1" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="95" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A95" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="96" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A96" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="97" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A97" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="98" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A98" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="99" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A99" s="1" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="100" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A100" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="101" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A101" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="102" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A102" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="103" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A103" s="1" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="104" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A104" s="1" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="105" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A105" s="1" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="106" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A106" s="1" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="107" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A107" s="1" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="108" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A108" s="1" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="109" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A109" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="110" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A110" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="111" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A111" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="112" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A112" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="113" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A113" s="1" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="114" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A114" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="115" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A115" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="116" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A116" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="117" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A117" s="1" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="118" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A118" s="1" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="119" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A119" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="120" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A120" s="1" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="121" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A121" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="122" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A122" s="1" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="123" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A123" s="1" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="124" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A124" s="1" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="125" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A125" s="1" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="126" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A126" s="1" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="127" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A127" s="1" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="128" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A128" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="129" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A129" s="1" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="130" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A130" s="1" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="131" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A131" s="1" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="132" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A132" s="1" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="133" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A133" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="134" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A134" s="1" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="135" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A135" s="1" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="136" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A136" s="1" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="137" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A137" s="1" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="138" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A138" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="139" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A139" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="140" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A140" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="141" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A141" s="1" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="142" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A142" s="1" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="143" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A143" s="1" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="144" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A144" s="1" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="145" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A145" s="1" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="146" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A146" s="1" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="147" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A147" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="148" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A148" s="1" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="149" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A149" s="1" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="150" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A150" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="151" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A151" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="152" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A152" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="153" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A153" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="154" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A154" s="1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="155" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A155" s="1" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="156" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A156" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="157" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A157" s="1" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="158" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A158" s="1" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="159" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A159" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="160" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A160" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="161" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A161" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="162" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A162" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="163" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A163" s="1" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="164" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A164" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="165" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A165" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="166" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A166" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="167" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A167" s="1" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="168" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A168" s="1" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="169" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A169" s="1" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="170" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A170" s="1" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="171" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A171" s="1" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="172" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A172" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="173" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A173" s="1" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="174" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A174" s="1" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="175" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A175" s="1" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="176" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A176" s="1" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="177" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A177" s="1" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="178" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A178" s="1" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="179" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A179" s="1" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="180" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A180" s="1" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="181" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A181" s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="182" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A182" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="183" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A183" s="1" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="184" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A184" s="1" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="185" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A185" s="1" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="186" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A186" s="1" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="187" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A187" s="1" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="188" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A188" s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="189" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A189" s="1" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="190" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A190" s="1" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="191" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A191" s="1" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="192" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A192" s="1" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="193" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A193" s="1" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="194" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A194" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="195" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A195" s="1" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="196" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A196" s="1" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="197" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A197" s="1" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="198" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A198" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="199" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A199" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="200" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A200" s="1" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="201" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A201" s="1" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="202" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A202" s="1" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="203" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A203" s="1" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="204" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A204" s="1" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="205" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A205" s="1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="206" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A206" s="1" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="207" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A207" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="208" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A208" s="1" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row r="209" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A209" s="1" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="210" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A210" s="1" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="211" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A211" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
     </row>
     <row r="212" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A212" s="1" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
     <row r="213" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A213" s="1" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="214" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A214" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
     </row>
     <row r="215" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A215" s="1" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="216" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A216" s="1" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
     </row>
     <row r="217" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A217" s="1" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="218" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A218" s="1" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
     </row>
     <row r="219" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A219" s="1" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
     <row r="220" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A220" s="1" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="221" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A221" s="1" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="222" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A222" s="1" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="223" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A223" s="1" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="224" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A224" s="1" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="225" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A225" s="1" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="226" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A226" s="1" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="227" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A227" s="1" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="228" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A228" s="1" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
     <row r="229" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A229" s="1" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
     </row>
     <row r="230" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A230" s="1" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
     </row>
     <row r="231" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A231" s="1" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="232" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A232" s="1" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
     </row>
     <row r="233" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A233" s="1" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
     </row>
     <row r="234" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A234" s="1" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="235" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A235" s="1" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="236" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A236" s="1" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
     </row>
     <row r="237" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A237" s="1" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
     </row>
     <row r="238" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A238" s="1" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="239" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A239" s="1" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="240" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A240" s="1" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
     </row>
     <row r="241" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A241" s="1" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="242" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A242" s="1" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
     </row>
     <row r="243" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A243" s="1" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
     </row>
     <row r="244" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A244" s="1" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
   </sheetData>
